--- a/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H367"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -474,7 +474,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -489,7 +489,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.delinquent[1]</t>
+          <t xml:space="preserve">atk.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -506,7 +506,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -521,7 +521,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.delinquent[2]</t>
+          <t xml:space="preserve">atk.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -538,7 +538,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -553,7 +553,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.delinquent[3]</t>
+          <t xml:space="preserve">atk.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -570,7 +570,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.delinquent[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.bold[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -585,7 +585,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.delinquent[4]</t>
+          <t xml:space="preserve">atk.delinquent.bold[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -602,7 +602,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -617,7 +617,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.delinquent[1]</t>
+          <t xml:space="preserve">bigmove.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -634,7 +634,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -649,7 +649,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.delinquent[2]</t>
+          <t xml:space="preserve">bigmove.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -666,7 +666,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -681,7 +681,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.delinquent[3]</t>
+          <t xml:space="preserve">bigmove.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -698,7 +698,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -713,7 +713,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.delinquent[1]</t>
+          <t xml:space="preserve">climax.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -730,7 +730,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -745,7 +745,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.delinquent[2]</t>
+          <t xml:space="preserve">climax.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -762,7 +762,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -794,7 +794,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -809,7 +809,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -826,7 +826,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -841,7 +841,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -858,7 +858,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -873,7 +873,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold.delinquent[1]</t>
+          <t xml:space="preserve">badWinner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -890,7 +890,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -905,7 +905,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold.delinquent[1]</t>
+          <t xml:space="preserve">goodWinner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -922,7 +922,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -937,7 +937,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -954,7 +954,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -969,7 +969,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -986,7 +986,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold.delinquent[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1018,7 +1018,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold.delinquent[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.delinquent[2]</t>
+          <t xml:space="preserve">loser.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -1050,7 +1050,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -1082,7 +1082,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold.delinquent[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.delinquent[2]</t>
+          <t xml:space="preserve">winner.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1114,7 +1114,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.delinquent[1]</t>
+          <t xml:space="preserve">competition_won.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1146,7 +1146,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.delinquent[2]</t>
+          <t xml:space="preserve">competition_won.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1178,7 +1178,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.delinquent[1]</t>
+          <t xml:space="preserve">direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1210,7 +1210,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.delinquent[2]</t>
+          <t xml:space="preserve">direct.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1242,7 +1242,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.delinquent[1]</t>
+          <t xml:space="preserve">fa_signing.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1274,7 +1274,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.delinquent[2]</t>
+          <t xml:space="preserve">fa_signing.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1306,7 +1306,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.delinquent.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.bold.hit[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.hit[1]</t>
+          <t xml:space="preserve">delinquent.bold.hit[1]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1338,7 +1338,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.delinquent.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.bold.hit[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.hit[2]</t>
+          <t xml:space="preserve">delinquent.bold.hit[2]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1370,7 +1370,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.delinquent.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.bold.win[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.win[1]</t>
+          <t xml:space="preserve">delinquent.bold.win[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1402,7 +1402,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.delinquent.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.bold.win[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.win[2]</t>
+          <t xml:space="preserve">delinquent.bold.win[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1434,7 +1434,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1466,7 +1466,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1498,7 +1498,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1530,7 +1530,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1562,7 +1562,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1594,7 +1594,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1626,7 +1626,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1658,7 +1658,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1690,7 +1690,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1722,7 +1722,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1754,7 +1754,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1786,7 +1786,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1818,7 +1818,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1850,7 +1850,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1882,7 +1882,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1914,7 +1914,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1946,7 +1946,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.bold.delinquent[1]</t>
+          <t xml:space="preserve">ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1978,7 +1978,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.bold.delinquent[1]</t>
+          <t xml:space="preserve">behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -2010,7 +2010,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -2042,7 +2042,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2074,7 +2074,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2106,7 +2106,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2138,7 +2138,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2170,7 +2170,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2202,7 +2202,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2234,7 +2234,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2266,7 +2266,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2298,7 +2298,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.delinquent[1]</t>
+          <t xml:space="preserve">winnerLines.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2330,7 +2330,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2362,7 +2362,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2394,7 +2394,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.delinquent[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2426,7 +2426,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.delinquent[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold.delinquent[1]</t>
+          <t xml:space="preserve">awakening.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -3226,7 +3226,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.delinquent[1]</t>
+          <t xml:space="preserve">accepted.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3258,7 +3258,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.delinquent[1]</t>
+          <t xml:space="preserve">defended.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3290,7 +3290,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.delinquent[1]</t>
+          <t xml:space="preserve">defense_failed.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3322,7 +3322,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.delinquent[1]</t>
+          <t xml:space="preserve">default.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3354,7 +3354,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.delinquent[1]</t>
+          <t xml:space="preserve">former_champ.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3386,7 +3386,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3418,7 +3418,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.delinquent[1]</t>
+          <t xml:space="preserve">high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3450,7 +3450,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.delinquent[1]</t>
+          <t xml:space="preserve">accept_former_champ.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3482,7 +3482,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">accept_heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3514,7 +3514,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.delinquent[1]</t>
+          <t xml:space="preserve">accept_no_title.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3546,7 +3546,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.delinquent[1]</t>
+          <t xml:space="preserve">accept_terminal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3578,7 +3578,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.delinquent[1]</t>
+          <t xml:space="preserve">accept_winless.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3610,7 +3610,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.delinquent[1]</t>
+          <t xml:space="preserve">refuse_champ.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3642,7 +3642,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.delinquent[1]</t>
+          <t xml:space="preserve">refuse_distrust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3674,7 +3674,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.delinquent[1]</t>
+          <t xml:space="preserve">refuse_fighting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3706,7 +3706,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">refuse_heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3738,7 +3738,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">A1_champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3770,7 +3770,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.delinquent[1]</t>
+          <t xml:space="preserve">A2_uncrowned.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3802,7 +3802,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.delinquent[1]</t>
+          <t xml:space="preserve">A3_heel.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3834,7 +3834,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.delinquent[1]</t>
+          <t xml:space="preserve">A4_veteran.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3866,7 +3866,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.delinquent[1]</t>
+          <t xml:space="preserve">B1_young.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3898,7 +3898,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.delinquent[1]</t>
+          <t xml:space="preserve">B2_prime.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3930,7 +3930,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.delinquent[1]</t>
+          <t xml:space="preserve">B3_older.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3962,7 +3962,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_champion_injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3994,7 +3994,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -4026,7 +4026,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.delinquent[1]</t>
+          <t xml:space="preserve">raise_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4058,7 +4058,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4090,7 +4090,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4122,7 +4122,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.delinquent[1]</t>
+          <t xml:space="preserve">raise_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4154,7 +4154,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.delinquent[1]</t>
+          <t xml:space="preserve">raise_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4186,7 +4186,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.delinquent[1]</t>
+          <t xml:space="preserve">sudden_departure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4218,7 +4218,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.delinquent[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.delinquent[2]</t>
+          <t xml:space="preserve">sudden_departure.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4250,7 +4250,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.delinquent[1]</t>
+          <t xml:space="preserve">transfer_listen.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4282,7 +4282,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.delinquent[1]</t>
+          <t xml:space="preserve">transfer_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4314,7 +4314,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.delinquent[1]</t>
+          <t xml:space="preserve">transfer_release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4346,7 +4346,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.delinquent[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4378,7 +4378,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.delinquent[1]</t>
+          <t xml:space="preserve">transfer_retain_success.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4410,7 +4410,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.bold.delinquent[1]</t>
+          <t xml:space="preserve">blocked.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4443,7 +4443,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.bold.delinquent[1]</t>
+          <t xml:space="preserve">fail.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4476,7 +4476,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold.delinquent[1]</t>
+          <t xml:space="preserve">start.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4509,7 +4509,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.bold.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.bold.delinquent[1]</t>
+          <t xml:space="preserve">success.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -5726,22 +5726,22 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_FOLLOWER_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.delinquent</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_FOLLOWER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bold.attack.delinquent</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5751,29 +5751,29 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へっ、別に頼まれたわけじゃねーけど。ま、付き合ってやるよ。</t>
+          <t xml:space="preserve">もう、一緒にゃいられねえ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.delinquent</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bold.defend.delinquent</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5783,14 +5783,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……仕方ねえな。あんたらのケツ、あたしが持ってやるよ。</t>
+          <t xml:space="preserve">上等だ、かかってこい</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F01_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5815,14 +5815,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰に文句言われても、あたしが前で受ける。引っ込んでな。</t>
+          <t xml:space="preserve">舐めてんじゃねーぞって話だよ。毎回毎回、同じパターンで。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5847,29 +5847,29 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつらと馴れ合う気なんかねえよ。道を分けるだけだ。</t>
+          <t xml:space="preserve">……ったく、気まずいっての。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.delinquent</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.delinquent</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5879,29 +5879,29 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、一緒にゃいられねえ</t>
+          <t xml:space="preserve">上等じゃねーか。来いよ、いつでも。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.delinquent</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_high[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.delinquent</t>
+          <t xml:space="preserve">delinquent.bold.hp_high[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5911,14 +5911,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等だ、かかってこい</t>
+          <t xml:space="preserve">チッ……負けた。今日のとこはな</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_low[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold.hp_low[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5943,14 +5943,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……チッ。あの人がいねえリングなんて、想像つかねえよ。</t>
+          <t xml:space="preserve">（息も荒い）</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_mid[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold.hp_mid[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5975,14 +5975,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……義理とか、もう重てえんだよ。</t>
+          <t xml:space="preserve">……うるせえ……</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6007,14 +6007,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めてんじゃねーぞって話だよ。毎回毎回、同じパターンで。</t>
+          <t xml:space="preserve">口ほどにもねえな、あんたの組</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6039,14 +6039,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ったく、気まずいっての。</t>
+          <t xml:space="preserve">次の番、誰だよ？　全員かかってこい</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6071,14 +6071,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい社長、あんた誰のおかげで食えてると思ってんだ？</t>
+          <t xml:space="preserve">ふん。あたしの勝ちだ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6103,14 +6103,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等じゃねーか。来いよ、いつでも。</t>
+          <t xml:space="preserve">今夜、あんたの組は終わる。しっかり見とけよ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.bold.delinquent.hp_high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.hp_high[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……負けた。今日のとこはな</t>
+          <t xml:space="preserve">ヘラヘラしてられんのも今のうちだぜ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.bold.delinquent.hp_low[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[3]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.hp_low[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[3]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6167,14 +6167,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（息も荒い）</t>
+          <t xml:space="preserve">舐めた口きいてた連中、ぜんぶ纏めてあたしが叩く</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.bold.delinquent.hp_mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.hp_mid[1]</t>
+          <t xml:space="preserve">delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6199,14 +6199,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うるせえ……</t>
+          <t xml:space="preserve">黙って来な。話すことなんかねえだろ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">口ほどにもねえな、あんたの組</t>
+          <t xml:space="preserve">おう、待ってたぞ。逃がさねえからな</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.bold.delinquent.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[2]</t>
+          <t xml:space="preserve">delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の番、誰だよ？　全員かかってこい</t>
+          <t xml:space="preserve">あたしんとこも、舐められたまま終わる気はねえ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.bold.delinquent.mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.mid[1]</t>
+          <t xml:space="preserve">delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6295,14 +6295,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん。あたしの勝ちだ</t>
+          <t xml:space="preserve">ったく。来るなら来いよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6327,14 +6327,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜、あんたの組は終わる。しっかり見とけよ</t>
+          <t xml:space="preserve">完全勝利だ。文句あるか？</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.bold.delinquent.high[2]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[2]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6359,14 +6359,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ヘラヘラしてられんのも今のうちだぜ</t>
+          <t xml:space="preserve">次。次出てこい</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.bold.delinquent.high[3]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[3]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6391,14 +6391,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めた口きいてた連中、ぜんぶ纏めてあたしが叩く</t>
+          <t xml:space="preserve">全員揃ってるな？ じゃあ、今夜が最後だ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.bold.delinquent.mid[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.mid[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙って来な。話すことなんかねえだろ</t>
+          <t xml:space="preserve">来なよ。全員でかかってこい</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6455,14 +6455,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、待ってたぞ。逃がさねえからな</t>
+          <t xml:space="preserve">黙って退け、なんて言わねえ。リングで証明してやる</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.bold.delinquent.high[2]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[2]</t>
+          <t xml:space="preserve">delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6487,238 +6487,238 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしんとこも、舐められたまま終わる気はねえ</t>
+          <t xml:space="preserve">あたしが上に立つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.bold.delinquent.mid[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.mid[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ったく。来るなら来いよ</t>
+          <t xml:space="preserve">当然だろ！ まだまだこんなもんじゃねーぜ！</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完全勝利だ。文句あるか？</t>
+          <t xml:space="preserve">（…体が勝手に動きやがる。これが限界の先かよ——）</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次。次出てこい</t>
+          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員揃ってるな？ じゃあ、今夜が最後だ</t>
+          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来なよ。全員でかかってこい</t>
+          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.bold.delinquent.high[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[1]</t>
+          <t xml:space="preserve">cap_reached.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙って退け、なんて言わねえ。リングで証明してやる</t>
+          <t xml:space="preserve">クソ、ここが限界かよ…でも、まだ他で勝負できる</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.bold.delinquent.high[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent.high[2]</t>
+          <t xml:space="preserve">ovr_elite.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが上に立つ。それだけだ</t>
+          <t xml:space="preserve">見えてきたぜ、てっぺんが！</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">ovr_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6743,14 +6743,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然だろ！ まだまだこんなもんじゃねーぜ！</t>
+          <t xml:space="preserve">ここからだっつーの！ まだ全然足りねえ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">ovr_legend.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6775,14 +6775,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…体が勝手に動きやがる。これが限界の先かよ——）</t>
+          <t xml:space="preserve">てっぺんだ！ 文句あるやつは掛かってこい！</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.bold.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.bold.delinquent[1]</t>
+          <t xml:space="preserve">pop_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6807,14 +6807,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
+          <t xml:space="preserve">やっと気づいたか！ もっと見とけよ！</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.bold.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.bold.delinquent[1]</t>
+          <t xml:space="preserve">pop_star.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6839,14 +6839,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
+          <t xml:space="preserve">全員まとめて最高の試合見せてやるぜ！</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.bold.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6871,14 +6871,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
+          <t xml:space="preserve">…燃えねーんだよ。何やっても、火がつかねー</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6903,14 +6903,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">クソ、ここが限界かよ…でも、まだ他で勝負できる</t>
+          <t xml:space="preserve">目ぇ覚めたぜ。ここで終わるかよ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6935,14 +6935,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見えてきたぜ、てっぺんが！</t>
+          <t xml:space="preserve">待たせたな！ ここからだぜ！</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.delinquent[1]</t>
+          <t xml:space="preserve">defeat.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6967,14 +6967,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからだっつーの！ まだ全然足りねえ</t>
+          <t xml:space="preserve">…チッ、何やってんだよあたし</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.delinquent[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6999,14 +6999,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんだ！ 文句あるやつは掛かってこい！</t>
+          <t xml:space="preserve">治ったっつーのに…何でもたついてんだ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold.delinquent[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7031,14 +7031,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと気づいたか！ もっと見とけよ！</t>
+          <t xml:space="preserve">あたしがビビってる？ ふざけんな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.delinquent[1]</t>
+          <t xml:space="preserve">penalty_end.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7063,14 +7063,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめて最高の試合見せてやるぜ！</t>
+          <t xml:space="preserve">体は万全なのに…気持ちがついてこねー</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7080,29 +7080,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えねーんだよ。何やっても、火がつかねー</t>
+          <t xml:space="preserve">殴って殴られて、最後に立ってた。それだけだ。…最高だったけどな</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7112,29 +7112,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目ぇ覚めたぜ。ここで終わるかよ</t>
+          <t xml:space="preserve">最強はあたしだ。証拠がここにある。文句は拳で言いに来い</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7144,29 +7144,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待たせたな！ ここからだぜ！</t>
+          <t xml:space="preserve">やりたい放題やって、全部勝ち取った。最高の人生だ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7176,29 +7176,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.delinquent[1]</t>
+          <t xml:space="preserve">mediaAward.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ、何やってんだよあたし</t>
+          <t xml:space="preserve">よっしゃ！ 来年はもっとやったるぞ！</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7208,29 +7208,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.delinquent[1]</t>
+          <t xml:space="preserve">mvp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">治ったっつーのに…何でもたついてんだ</t>
+          <t xml:space="preserve">一番強かったのはあたしだ。文句あるなら来いよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7240,29 +7240,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.delinquent[1]</t>
+          <t xml:space="preserve">rookie.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしがビビってる？ ふざけんな</t>
+          <t xml:space="preserve">ハッ、新人なのは今年だけだ。来年は全部かっさらう</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7272,29 +7272,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全なのに…気持ちがついてこねー</t>
+          <t xml:space="preserve">おうっ、ドームだろうが関係ねえ。ぶっ壊すだけだ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7319,14 +7319,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殴って殴られて、最後に立ってた。それだけだ。…最高だったけどな</t>
+          <t xml:space="preserve">ここが最後じゃねえ。まだ先、あるからな</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7351,14 +7351,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強はあたしだ。証拠がここにある。文句は拳で言いに来い</t>
+          <t xml:space="preserve">…全員ひっくり返してやる。見てろよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7383,14 +7383,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりたい放題やって、全部勝ち取った。最高の人生だ</t>
+          <t xml:space="preserve">…全員、ひっくり返せた気がすんな。満員にしやがって</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7415,14 +7415,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ！ 来年はもっとやったるぞ！</t>
+          <t xml:space="preserve">くっそおおお、やってやったぜドーム満員!!</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7447,14 +7447,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番強かったのはあたしだ。文句あるなら来いよ</t>
+          <t xml:space="preserve">…覚えとけよ、観客全員。またぶっ壊しに来るからな</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7464,29 +7464,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.delinquent[1]</t>
+          <t xml:space="preserve">N1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ハッ、新人なのは今年だけだ。来年は全部かっさらう</t>
+          <t xml:space="preserve">まだ足りねえ。もっとやれるはずだ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7496,29 +7496,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">N2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おうっ、ドームだろうが関係ねえ。ぶっ壊すだけだ</t>
+          <t xml:space="preserve">あいつがいるから燃えるんだよ！</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7528,29 +7528,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">N3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最後じゃねえ。まだ先、あるからな</t>
+          <t xml:space="preserve">この程度で止まってられるかよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7560,29 +7560,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">N4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員ひっくり返してやる。見てろよ</t>
+          <t xml:space="preserve">この勢いで突っ走るぜ！</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7592,29 +7592,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員、ひっくり返せた気がすんな。満員にしやがって</t>
+          <t xml:space="preserve">…ここにいても、先が見えねえ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7624,29 +7624,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">N5_warning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそおおお、やってやったぜドーム満員!!</t>
+          <t xml:space="preserve">…最近、何のために戦ってんのか分かんねーんだ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.delinquent[3]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7656,29 +7656,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
+          <t xml:space="preserve">G1.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えとけよ、観客全員。またぶっ壊しに来るからな</t>
+          <t xml:space="preserve">…ふざけんなよ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.delinquent[1]</t>
+          <t xml:space="preserve">G2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7703,14 +7703,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りねえ。もっとやれるはずだ</t>
+          <t xml:space="preserve">…ガキが調子乗ってんじゃねーよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.delinquent[1]</t>
+          <t xml:space="preserve">G3.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7735,14 +7735,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつがいるから燃えるんだよ！</t>
+          <t xml:space="preserve">…いい加減使えよ。腐るぞ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.delinquent[1]</t>
+          <t xml:space="preserve">R2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7767,14 +7767,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まってられるかよ</t>
+          <t xml:space="preserve">…ハッ、群れるのは趣味じゃねーんだよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.delinquent[1]</t>
+          <t xml:space="preserve">R3.modal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7799,14 +7799,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢いで突っ走るぜ！</t>
+          <t xml:space="preserve">…チッ。…寂しいなんて言わねーけど</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.delinquent[1]</t>
+          <t xml:space="preserve">R4.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいても、先が見えねえ</t>
+          <t xml:space="preserve">…ザマァ見ろ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.delinquent[1]</t>
+          <t xml:space="preserve">R5.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7863,14 +7863,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近、何のために戦ってんのか分かんねーんだ</t>
+          <t xml:space="preserve">…クソッ…！</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7880,29 +7880,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">bonus.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふざけんなよ</t>
+          <t xml:space="preserve">おっしゃ！この金で栄養つけてもっと強くなるぜ！</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7912,29 +7912,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">camp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ガキが調子乗ってんじゃねーよ</t>
+          <t xml:space="preserve">やってやるぜ！帰る頃には別人だ！</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7944,29 +7944,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい加減使えよ。腐るぞ</t>
+          <t xml:space="preserve">アンタが信じてくれんなら、やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7976,29 +7976,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">encourage.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ハッ、群れるのは趣味じゃねーんだよ</t>
+          <t xml:space="preserve">止まってられるかよ！次は絶対やってやる！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8008,29 +8008,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.bold.delinquent[1]</t>
+          <t xml:space="preserve">faction_decree.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ。…寂しいなんて言わねーけど</t>
+          <t xml:space="preserve">ふざけんな。あそこは、あたしらの場所だっただろ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8040,29 +8040,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">media.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ザマァ見ろ</t>
+          <t xml:space="preserve">注目されんの大歓迎！やってやるぜ！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8072,29 +8072,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.bold.delinquent[1]</t>
+          <t xml:space="preserve">party.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…クソッ…！</t>
+          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.delinquent[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！この金で栄養つけてもっと強くなるぜ！</t>
+          <t xml:space="preserve">充電してくる！戻ったら全開だぜ！</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.delinquent[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8151,14 +8151,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！帰る頃には別人だ！</t>
+          <t xml:space="preserve">しゃあ！すぐ治して暴れに戻るぜ！</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.delinquent[1]</t>
+          <t xml:space="preserve">trainer.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8183,14 +8183,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">アンタが信じてくれんなら、やってやるよ！</t>
+          <t xml:space="preserve">最高じゃん！限界まで追い込んでもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.delinquent[1]</t>
+          <t xml:space="preserve">E1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まってられるかよ！次は絶対やってやる！</t>
+          <t xml:space="preserve">やってやるぜ！注目されんのは大歓迎だ！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold.delinquent[1]</t>
+          <t xml:space="preserve">E6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8247,14 +8247,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな。あそこは、あたしらの場所だっただろ</t>
+          <t xml:space="preserve">他所からいい話来てんだよ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8279,14 +8279,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目されんの大歓迎！やってやるぜ！</t>
+          <t xml:space="preserve">はぁ？やる気出ないっつの。文句あんなら試合組めよ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.delinquent[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8311,14 +8311,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
+          <t xml:space="preserve">（「なんであたしらがこんな扱い受けなきゃなんねぇんだよ」とロッカーで吠えている）</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.delinquent[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8343,14 +8343,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">充電してくる！戻ったら全開だぜ！</t>
+          <t xml:space="preserve">（SNSに「このまま終わる気はねぇから」と宣戦布告じみた投稿）</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold.delinquent[1]</t>
+          <t xml:space="preserve">S1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃあ！すぐ治して暴れに戻るぜ！</t>
+          <t xml:space="preserve">ベルトよこせ！今すぐ組め！</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.delinquent[1]</t>
+          <t xml:space="preserve">S2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8407,14 +8407,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高じゃん！限界まで追い込んでもらうぜ！</t>
+          <t xml:space="preserve">あいつと決着つけさせろ！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.delinquent[1]</t>
+          <t xml:space="preserve">S3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8439,14 +8439,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！注目されんのは大歓迎だ！</t>
+          <t xml:space="preserve">くそ…体がもう限界だ。休ませてくれ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.delinquent[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8471,14 +8471,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話来てんだよ。考えさせてくれ</t>
+          <t xml:space="preserve">こんなんじゃやってらんねーよ！改善しろ！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.delinquent[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8503,14 +8503,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ？やる気出ないっつの。文句あんなら試合組めよ</t>
+          <t xml:space="preserve">…………（舌打ちをこらえて、拳を握っている）</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.bold.delinquent[1]</t>
+          <t xml:space="preserve">S5.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8535,14 +8535,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「なんであたしらがこんな扱い受けなきゃなんねぇんだよ」とロッカーで吠えている）</t>
+          <t xml:space="preserve">もっと強くなりてぇ！特訓させろ！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.bold.delinquent[1]</t>
+          <t xml:space="preserve">S6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8567,14 +8567,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わる気はねぇから」と宣戦布告じみた投稿）</t>
+          <t xml:space="preserve">後輩の面倒は任せろ。鍛えてやる</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.delinquent[1]</t>
+          <t xml:space="preserve">B1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8599,14 +8599,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトよこせ！今すぐ組め！</t>
+          <t xml:space="preserve">くそっ…こんなとこで止まってらんねえ！</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8631,14 +8631,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつと決着つけさせろ！</t>
+          <t xml:space="preserve">あいつの態度が気に食わねえ！限界だ！</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がもう限界だ。休ませてくれ</t>
+          <t xml:space="preserve">黙ってると思うなよ！向こうが謝れ！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8695,14 +8695,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんじゃやってらんねーよ！改善しろ！</t>
+          <t xml:space="preserve">コラボ商品、派手にやってやる！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8727,14 +8727,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（舌打ちをこらえて、拳を握っている）</t>
+          <t xml:space="preserve">CM？ 全国にこの顔を売りつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_fan.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりてぇ！特訓させろ！</t>
+          <t xml:space="preserve">ファンイベ、盛り上げてやるよ！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8791,14 +8791,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒は任せろ。鍛えてやる</t>
+          <t xml:space="preserve">歩くだけなら怖くない。ど派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8823,14 +8823,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…こんなとこで止まってらんねえ！</t>
+          <t xml:space="preserve">グラビアも勝負事だ。全力でいくよ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつの態度が気に食わねえ！限界だ！</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 絶対爪痕残す！</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.delinquent[1]</t>
+          <t xml:space="preserve">B4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってると思うなよ！向こうが謝れ！</t>
+          <t xml:space="preserve">全国に見せてやるぜ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8904,29 +8904,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品、派手にやってやる！</t>
+          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8936,29 +8936,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？ 全国にこの顔を売りつけてやる！</t>
+          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8968,29 +8968,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンイベ、盛り上げてやるよ！</t>
+          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9000,29 +9000,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">歩くだけなら怖くない。ど派手にやってやる</t>
+          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9032,29 +9032,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアも勝負事だ。全力でいくよ</t>
+          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9064,29 +9064,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 絶対爪痕残す！</t>
+          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9096,29 +9096,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見せてやるぜ！かかってこい！</t>
+          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9143,14 +9143,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
+          <t xml:space="preserve">もう決着はついてんだよ。何度潰されりゃ気が済む</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9175,14 +9175,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
+          <t xml:space="preserve">あの日から一度も、まともに寝てねえんだよ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9192,12 +9192,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">draftInterest.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9207,14 +9207,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
+          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9239,14 +9239,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
+          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9271,14 +9271,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
+          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9303,14 +9303,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
+          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">faSigning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9335,14 +9335,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
+          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.bold.delinquent[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9367,14 +9367,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう決着はついてんだよ。何度潰されりゃ気が済む</t>
+          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.bold.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9399,14 +9399,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの日から一度も、まともに寝てねえんだよ</t>
+          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9431,14 +9431,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
+          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.delinquent[1]</t>
+          <t xml:space="preserve">heatSelf.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9463,14 +9463,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
+          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.delinquent[2]</t>
+          <t xml:space="preserve">injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9495,14 +9495,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
+          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold.delinquent[1]</t>
+          <t xml:space="preserve">injury.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9527,14 +9527,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.delinquent[1]</t>
+          <t xml:space="preserve">release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9559,14 +9559,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
+          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.delinquent[1]</t>
+          <t xml:space="preserve">release.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9591,14 +9591,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
+          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.bold.delinquent[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9623,14 +9623,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
+          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.bold.delinquent[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9655,14 +9655,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
+          <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.bold.delinquent[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9687,14 +9687,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
+          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.delinquent[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9719,14 +9719,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
+          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.delinquent[2]</t>
+          <t xml:space="preserve">titleLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9751,14 +9751,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
+          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.delinquent[1]</t>
+          <t xml:space="preserve">titleWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
+          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9815,14 +9815,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
+          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9847,14 +9847,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
+          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9879,14 +9879,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
+          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9918,7 +9918,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9950,7 +9950,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9982,7 +9982,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10014,7 +10014,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10024,29 +10024,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
+          <t xml:space="preserve">虫が好かねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10056,29 +10056,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
+          <t xml:space="preserve">おい、最近態度おかしくね？ ムカつくな</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10088,29 +10088,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
+          <t xml:space="preserve">見込みあるよ。面倒見てやるか</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10120,29 +10120,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.delinquent[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
+          <t xml:space="preserve">フン、気に入ったぜ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10152,29 +10152,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
+          <t xml:space="preserve">相棒だ。文句あるか</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10184,29 +10184,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
+          <t xml:space="preserve">時代は終わりだ。もう眼中にねぇ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10216,29 +10216,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
+          <t xml:space="preserve">面ぁ見ると血が騒ぐんだよ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10263,14 +10263,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">虫が好かねぇんだよ</t>
+          <t xml:space="preserve">這いつくばらせてやる…！</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10295,14 +10295,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近態度おかしくね？ ムカつくな</t>
+          <t xml:space="preserve">生涯の敵だ。最後まで殴り合ってやる</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10327,14 +10327,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込みあるよ。面倒見てやるか</t>
+          <t xml:space="preserve">ここは最高だ。あたしがてっぺんまで連れてってやるよ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.delinquent[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10359,14 +10359,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フン、気に入ったぜ</t>
+          <t xml:space="preserve">あたしを舐めてんなら出てってやるよ。後悔するなよ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10391,14 +10391,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒だ。文句あるか</t>
+          <t xml:space="preserve">なめんじゃねぇぞ。あたしをもっと使え</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.loss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10423,14 +10423,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時代は終わりだ。もう眼中にねぇ</t>
+          <t xml:space="preserve">次会ったらぶっ飛ばしてやる…覚えてろ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10455,14 +10455,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面ぁ見ると血が騒ぐんだよ</t>
+          <t xml:space="preserve">へっ、雑魚が。話にならねぇ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10487,14 +10487,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">這いつくばらせてやる…！</t>
+          <t xml:space="preserve">おらおら、休んでる暇ねぇぞ！</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10519,14 +10519,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">生涯の敵だ。最後まで殴り合ってやる</t>
+          <t xml:space="preserve">ダチだ。大事にしてやるよ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10551,14 +10551,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは最高だ。あたしがてっぺんまで連れてってやるよ</t>
+          <t xml:space="preserve">超えるまで止まらねぇ</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-06.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10583,14 +10583,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしを舐めてんなら出てってやるよ。後悔するなよ</t>
+          <t xml:space="preserve">おいこら！ あたしを出せよ！ 暴れたいんだよ！</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-07.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10615,14 +10615,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なめんじゃねぇぞ。あたしをもっと使え</t>
+          <t xml:space="preserve">くそっ、こんな体じゃ戦えねぇだろ…！</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10647,14 +10647,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次会ったらぶっ飛ばしてやる…覚えてろ</t>
+          <t xml:space="preserve">ふざけんな…いつまで負けてんだよ…！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-09.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10679,14 +10679,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へっ、雑魚が。話にならねぇ</t>
+          <t xml:space="preserve">止まらねぇぜ！ 全員ぶっ倒す！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.bold.delinquent[1]</t>
+          <t xml:space="preserve">GL-10.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10711,14 +10711,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おらおら、休んでる暇ねぇぞ！</t>
+          <t xml:space="preserve">チッ…じっとしてらんねぇ。もう走れるだろ…！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10743,14 +10743,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダチだ。大事にしてやるよ</t>
+          <t xml:space="preserve">調子戻っちまったけど、あの感覚は覚えたぜ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10760,29 +10760,29 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.bold.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えるまで止まらねぇ</t>
+          <t xml:space="preserve">身体? 知るかよ。最後まで残ったんだ、テッペン獲るに決まってんだろ</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10792,29 +10792,29 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.bold.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おいこら！ あたしを出せよ！ 暴れたいんだよ！</t>
+          <t xml:space="preserve">ボロボロだろうが関係ねえ。この一戦、ぶっ潰して終わらせる</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10824,29 +10824,29 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.bold.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ、こんな体じゃ戦えねぇだろ…！</t>
+          <t xml:space="preserve">痛え? あたりめえだろ。でもここで倒れたら、今までが無駄になる。行くぞ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10856,29 +10856,29 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.bold.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…いつまで負けてんだよ…！</t>
+          <t xml:space="preserve">相手は誰だ! 何人来ようがまとめてかかってこいや</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10888,29 +10888,29 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.bold.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まらねぇぜ！ 全員ぶっ倒す！</t>
+          <t xml:space="preserve">一人ずつしか来れねえのか? じれってえな。全員まとめて潰してやる</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10920,29 +10920,29 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.bold.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ…じっとしてらんねぇ。もう走れるだろ…！</t>
+          <t xml:space="preserve">このリング、渡すわけねえだろ。出てこいよ、順番に沈めてやる</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10952,29 +10952,29 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子戻っちまったけど、あの感覚は覚えたぜ</t>
+          <t xml:space="preserve">一人ぶっ倒した! …はぁ、まだいけるぞ。次、どいつだ、出てこい!</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.delinquent[1]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10999,14 +10999,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体? 知るかよ。最後まで残ったんだ、テッペン獲るに決まってんだろ</t>
+          <t xml:space="preserve">まだ終わってねえ! このリング、渡すかよ。次、さっさとかかってこい!</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.delinquent[2]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11031,14 +11031,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボロボロだろうが関係ねえ。この一戦、ぶっ潰して終わらせる</t>
+          <t xml:space="preserve">一人沈めたぞ! …はぁ、はぁ…まだ足りねえ。次、誰でもいい、来い!</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.delinquent[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.delinquent[3]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11063,14 +11063,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛え? あたりめえだろ。でもここで倒れたら、今までが無駄になる。行くぞ</t>
+          <t xml:space="preserve">あたしらが最強だ。文句あんなら、かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11095,14 +11095,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ! 何人来ようがまとめてかかってこいや</t>
+          <t xml:space="preserve">三人揃って無敵だったな。最高のチームだぜ</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.delinquent[2]</t>
+          <t xml:space="preserve">defiant.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11127,14 +11127,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつしか来れねえのか? じれってえな。全員まとめて潰してやる</t>
+          <t xml:space="preserve">MVP？ はっ、こんなもんじゃ足りねえよ。次は丸ごとぶん取る</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.delinquent[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11144,12 +11144,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.delinquent[3]</t>
+          <t xml:space="preserve">defiant.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11159,14 +11159,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、渡すわけねえだろ。出てこいよ、順番に沈めてやる</t>
+          <t xml:space="preserve">賞はもらっとくけど、次は優勝旗ごと叩き取る。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.delinquent[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11191,14 +11191,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒した! …はぁ、まだいけるぞ。次、どいつだ、出てこい!</t>
+          <t xml:space="preserve">来るだけ来いっつったろ？ 全員ぶっ倒して、まだ余裕あんぞ</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.delinquent[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11223,14 +11223,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえ! このリング、渡すかよ。次、さっさとかかってこい!</t>
+          <t xml:space="preserve">何人並ぼうが一緒だ。あたしの前に立つなら覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.delinquent[3]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.delinquent[3]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11255,14 +11255,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人沈めたぞ! …はぁ、はぁ…まだ足りねえ。次、誰でもいい、来い!</t>
+          <t xml:space="preserve">言ったろ？ テッペンは俺のもんだってな</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしらが最強だ。文句あんなら、かかってこいよ</t>
+          <t xml:space="preserve">はっ、当然の結果だぜ。誰にも負けねえ</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.delinquent[2]</t>
+          <t xml:space="preserve">postLose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11319,14 +11319,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人揃って無敵だったな。最高のチームだぜ</t>
+          <t xml:space="preserve">ふざけんな…！ 次は絶対ぶっ潰す！</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.delinquent[1]</t>
+          <t xml:space="preserve">postLose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11351,14 +11351,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ はっ、こんなもんじゃ足りねえよ。次は丸ごとぶん取る</t>
+          <t xml:space="preserve">こんなん認めねえ…！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.delinquent[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11383,14 +11383,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっとくけど、次は優勝旗ごと叩き取る。覚えとけ</t>
+          <t xml:space="preserve">はっ、楽勝だぜ。次も同じだ</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.delinquent[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11415,14 +11415,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るだけ来いっつったろ？ 全員ぶっ倒して、まだ余裕あんぞ</t>
+          <t xml:space="preserve">止められるもんなら止めてみろ</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.delinquent[2]</t>
+          <t xml:space="preserve">postWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11447,14 +11447,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人並ぼうが一緒だ。あたしの前に立つなら覚悟しろ</t>
+          <t xml:space="preserve">ちっ、まだ足りねえ。次は全員ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.delinquent[1]</t>
+          <t xml:space="preserve">postWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11479,14 +11479,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったろ？ テッペンは俺のもんだってな</t>
+          <t xml:space="preserve">まだ上がいるってのがムカつくぜ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.delinquent[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11511,14 +11511,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、当然の結果だぜ。誰にも負けねえ</t>
+          <t xml:space="preserve">ここまで来たからにゃ、テッペン獲るに決まってんだろ</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11543,14 +11543,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…！ 次は絶対ぶっ潰す！</t>
+          <t xml:space="preserve">最後の相手か。ぶっ壊してやるよ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.delinquent[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11575,14 +11575,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなん認めねえ…！</t>
+          <t xml:space="preserve">邪魔するヤツは全員ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11607,14 +11607,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、楽勝だぜ。次も同じだ</t>
+          <t xml:space="preserve">かかって来いよ。一発で沈めてやる</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.delinquent[2]</t>
+          <t xml:space="preserve">summon.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11639,14 +11639,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止められるもんなら止めてみろ</t>
+          <t xml:space="preserve">あァ？ まあいいけど。暴れる場所が増えるだけだ</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.delinquent[1]</t>
+          <t xml:space="preserve">summon.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11671,14 +11671,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ、まだ足りねえ。次は全員ぶっ倒す</t>
+          <t xml:space="preserve">うっせーな、勝手に呼びやがって。……まあ出るけど</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.delinquent[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11703,14 +11703,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ上がいるってのがムカつくぜ</t>
+          <t xml:space="preserve">ぶっ潰してやるぜ！泣いても知らねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.delinquent[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11735,14 +11735,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たからにゃ、テッペン獲るに決まってんだろ</t>
+          <t xml:space="preserve">やったぞ……！ 全員ぶっ倒してここまで来たんだ……！</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.delinquent[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11767,14 +11767,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の相手か。ぶっ壊してやるよ</t>
+          <t xml:space="preserve">てめえらの団体？ うちの新人にも勝てねえだろ</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.delinquent[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11799,14 +11799,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">邪魔するヤツは全員ぶっ倒す</t>
+          <t xml:space="preserve">ぶっ潰してやるよ。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.delinquent[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11831,14 +11831,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かかって来いよ。一発で沈めてやる</t>
+          <t xml:space="preserve">はっ、ザッコ。逃げんのかよ</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.delinquent[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11848,12 +11848,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11863,14 +11863,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あァ？ まあいいけど。暴れる場所が増えるだけだ</t>
+          <t xml:space="preserve">次会った時は逃がさねえからな。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.delinquent[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.delinquent[2]</t>
+          <t xml:space="preserve">result_lose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっせーな、勝手に呼びやがって。……まあ出るけど</t>
+          <t xml:space="preserve">ちっ…マジかよ…。絶対リベンジしてやる</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11927,14 +11927,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰してやるぜ！泣いても知らねーぞ！</t>
+          <t xml:space="preserve">ふざけんな…次はぶっ壊してやるからな</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.delinquent[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">result_win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11959,14 +11959,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぞ……！ 全員ぶっ倒してここまで来たんだ……！</t>
+          <t xml:space="preserve">はっ、楽勝だぜ。雑魚が調子乗んなよ</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.delinquent[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">result_win.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11991,14 +11991,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てめえらの団体？ うちの新人にも勝てねえだろ</t>
+          <t xml:space="preserve">これがウチの強さだ。分かったか</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.delinquent[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -12023,14 +12023,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰してやるよ。覚悟しろ</t>
+          <t xml:space="preserve">当然だろ！ うちの団体なめんじゃねえよ！</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.delinquent[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12055,14 +12055,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、ザッコ。逃げんのかよ</t>
+          <t xml:space="preserve">ざまあみろ！ これがうちの実力だ！</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.delinquent[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12087,14 +12087,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次会った時は逃がさねえからな。覚えとけ</t>
+          <t xml:space="preserve">うちの団体に手ぇ出すからだ。ざまぁみろ</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.delinquent[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12104,29 +12104,29 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.delinquent[1]</t>
+          <t xml:space="preserve">fighter.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…マジかよ…。絶対リベンジしてやる</t>
+          <t xml:space="preserve">てっぺん獲ったぜ！でもまだまだこれからだ！</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.delinquent[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12136,29 +12136,29 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…次はぶっ壊してやるからな</t>
+          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12168,251 +12168,27 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、楽勝だぜ。雑魚が調子乗んなよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="368" ht="40" customHeight="1">
-      <c r="A368" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_win.bold.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">これがウチの強さだ。分かったか</t>
-        </is>
-      </c>
-    </row>
-    <row r="369" ht="40" customHeight="1">
-      <c r="A369" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">当然だろ！ うちの団体なめんじゃねえよ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="370" ht="40" customHeight="1">
-      <c r="A370" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ざまあみろ！ これがうちの実力だ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="371" ht="40" customHeight="1">
-      <c r="A371" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.delinquent[3]</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.delinquent[3]</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">うちの団体に手ぇ出すからだ。ざまぁみろ</t>
-        </is>
-      </c>
-    </row>
-    <row r="372" ht="40" customHeight="1">
-      <c r="A372" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter.bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">てっぺん獲ったぜ！でもまだまだこれからだ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="373" ht="40" customHeight="1">
-      <c r="A373" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="374" ht="40" customHeight="1">
-      <c r="A374" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H374"/>
+  <autoFilter ref="A1:H367"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H367"/>
+  <dimension ref="A1:H369"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしの全部、くらいやがれ！</t>
+          <t xml:space="preserve">私の全部、くらいやがれ！</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ここからだ…あたしの時間だぜ）</t>
+          <t xml:space="preserve">（ここからだ…私の時間だぜ）</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取り合いになんのは当然だろ？ アタシなんだから</t>
+          <t xml:space="preserve">取り合いになんのは当然だろ？ 私なんだから</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切られたあたしが、あそこの選手を叩き潰した。文句あるか。</t>
+          <t xml:space="preserve">切られた私が、あそこの選手を叩き潰した。文句あるか。</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしの番だ！</t>
+          <t xml:space="preserve">私の番だ！</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…あたしのミスだ、{partner}。次は絶対、返してやる。</t>
+          <t xml:space="preserve">くそっ…私のミスだ、{partner}。次は絶対、返してやる。</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったな{partner}！ あたしらが組みゃ、負ける気がしねえ！</t>
+          <t xml:space="preserve">やったな{partner}！ 私らが組みゃ、負ける気がしねえ！</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たかよ！ {partner}とあたしのタッグ、最強だぜ！</t>
+          <t xml:space="preserve">見たかよ！ {partner}と私のタッグ、最強だぜ！</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お前は俺の誇りだ。これからも来いよ</t>
+          <t xml:space="preserve">お前は私の誇りだ。これからも来いよ</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あざっす! ……行ってきます。</t>
+          <t xml:space="preserve">あざっす！ ……行ってきます。</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったっす! ……ほら、言った通りでしょ。</t>
+          <t xml:space="preserve">勝ったっす！ ……ほら、言った通りでしょ。</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。社長、ありがとうございました。</t>
+          <t xml:space="preserve">きっちり勝ってきたっすよ。社長、ありがとうっす。</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってきました。……頼んだ甲斐、あったでしょ?</t>
+          <t xml:space="preserve">やってきました。……頼んだ甲斐、あったでしょ？</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしを選んだ時点で、勝負ありだろ。</t>
+          <t xml:space="preserve">私を選んだ時点で、勝負ありだろ。</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ? まだ全然終わってねぇだろ。</t>
+          <t xml:space="preserve">はぁ？ まだ全然終わってねぇだろ。</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかず? 冗談。続きやるぞ。</t>
+          <t xml:space="preserve">決着つかず？ 冗談。続きやるぞ。</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが邪魔だってのか？ はっきり言えよ</t>
+          <t xml:space="preserve">私が邪魔だってのか？ はっきり言えよ</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしがいなくなったらこの団体終わりだぜ</t>
+          <t xml:space="preserve">私がいなくなったらこの団体終わりだぜ</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしの時代だった。文句あるやつはかかってこい</t>
+          <t xml:space="preserve">私の時代だった。文句あるやつはかかってこい</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが今の仲間に背くと思ったか？
+          <t xml:space="preserve">私が今の仲間に背くと思ったか？
 甘ぇよ、帰れ</t>
         </is>
       </c>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここがあたしの居場所だ。
+          <t xml:space="preserve">ここが私の居場所だ。
 出直してきな</t>
         </is>
       </c>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしを引き抜く？
+          <t xml:space="preserve">私を引き抜く？
 面白ぇ度胸してんじゃねーか</t>
         </is>
       </c>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あたしらのこと、もうちょい大事にしてくんないっすか。</t>
+          <t xml:space="preserve">社長、私らのこと、もうちょい大事にしてくんないっすか。</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、次のメイン、あたしらでいきますよ。話、通してください。</t>
+          <t xml:space="preserve">社長、次のメイン、私らでいきますよ。話、通してください。</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あたしらの給料、見直してくれません? はっきり言って足りないっす。</t>
+          <t xml:space="preserve">社長、私らの給料、見直してくれません？ はっきり言って足りないっす。</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あたしらの働き、ちゃんと数えてんですか。はっきり言ってもらえます?</t>
+          <t xml:space="preserve">社長、私らの働き、ちゃんと数えてんですか。はっきり言ってもらえます？</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか、社長ありがとうございます! みんな喜びますよ。</t>
+          <t xml:space="preserve">マジっすか、社長ありがとうございます！ みんな喜びますよ。</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。励みになりますよ。</t>
+          <t xml:space="preserve">社長、あんがとっす。そう言われちゃ、気合い入るっすよ。</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。あたしから言っときます。</t>
+          <t xml:space="preserve">…っす、わかりました。私から言っときます。</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん。あたしの勝ちだ</t>
+          <t xml:space="preserve">ふん。私の勝ちだ</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めた口きいてた連中、ぜんぶ纏めてあたしが叩く</t>
+          <t xml:space="preserve">舐めた口きいてた連中、ぜんぶ纏めて私が叩く</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしんとこも、舐められたまま終わる気はねえ</t>
+          <t xml:space="preserve">わたしんとこも、舐められたまま終わる気はねえ</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが上に立つ。それだけだ</t>
+          <t xml:space="preserve">私が上に立つ。それだけだ</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ、何やってんだよあたし</t>
+          <t xml:space="preserve">…チッ、何やってんだよ私</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしがビビってる？ ふざけんな</t>
+          <t xml:space="preserve">私がビビってる？ ふざけんな</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7095,14 +7095,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殴って殴られて、最後に立ってた。それだけだ。…最高だったけどな</t>
+          <t xml:space="preserve">対抗戦の頂点はあたしたちだ。異論あるならまた来な。</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7127,14 +7127,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強はあたしだ。証拠がここにある。文句は拳で言いに来い</t>
+          <t xml:space="preserve">殴って殴られて、最後に立ってた。それだけだ。…最高だったけどな</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.delinquent.bold[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7159,14 +7159,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりたい放題やって、全部勝ち取った。最高の人生だ</t>
+          <t xml:space="preserve">最強は私だ。証拠がここにある。文句は拳で言いに来い</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.delinquent.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7191,14 +7191,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ！ 来年はもっとやったるぞ！</t>
+          <t xml:space="preserve">やりたい放題やって、全部勝ち取った。最高の人生だ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.delinquent.bold[1]</t>
+          <t xml:space="preserve">mediaAward.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7223,14 +7223,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番強かったのはあたしだ。文句あるなら来いよ</t>
+          <t xml:space="preserve">よっしゃ！ 来年はもっとやったるぞ！</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.delinquent.bold[1]</t>
+          <t xml:space="preserve">mvp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7255,14 +7255,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ハッ、新人なのは今年だけだ。来年は全部かっさらう</t>
+          <t xml:space="preserve">一番強かったのは私だ。文句あるなら来いよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">rookie.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7287,14 +7287,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おうっ、ドームだろうが関係ねえ。ぶっ壊すだけだ</t>
+          <t xml:space="preserve">ハッ、新人なのは今年だけだ。来年は全部かっさらう</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">springTagChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7319,14 +7319,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最後じゃねえ。まだ先、あるからな</t>
+          <t xml:space="preserve">見ただろ。あたしたちのタッグが一番強いんだよ。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[3]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7351,14 +7351,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員ひっくり返してやる。見てろよ</t>
+          <t xml:space="preserve">おうっ、ドームだろうが関係ねえ。ぶっ壊すだけだ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7383,14 +7383,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員、ひっくり返せた気がすんな。満員にしやがって</t>
+          <t xml:space="preserve">ここが最後じゃねえ。まだ先、あるからな</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7415,14 +7415,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそおおお、やってやったぜドーム満員!!</t>
+          <t xml:space="preserve">…全員ひっくり返してやる。見てろよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[3]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7447,14 +7447,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えとけよ、観客全員。またぶっ壊しに来るからな</t>
+          <t xml:space="preserve">…全員、ひっくり返せた気がすんな。満員にしやがって</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7464,29 +7464,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りねえ。もっとやれるはずだ</t>
+          <t xml:space="preserve">くっそおおお、やってやったぜドーム満員！！</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7496,29 +7496,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつがいるから燃えるんだよ！</t>
+          <t xml:space="preserve">…覚えとけよ、観客全員。またぶっ壊しに来るからな</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.delinquent.bold[1]</t>
+          <t xml:space="preserve">N1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7543,14 +7543,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まってられるかよ</t>
+          <t xml:space="preserve">まだ足りねえ。もっとやれるはずだ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.delinquent.bold[1]</t>
+          <t xml:space="preserve">N2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7575,14 +7575,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢いで突っ走るぜ！</t>
+          <t xml:space="preserve">あいつがいるから燃えるんだよ！</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.delinquent.bold[1]</t>
+          <t xml:space="preserve">N3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7607,14 +7607,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいても、先が見えねえ</t>
+          <t xml:space="preserve">この程度で止まってられるかよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.delinquent.bold[1]</t>
+          <t xml:space="preserve">N4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7639,14 +7639,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近、何のために戦ってんのか分かんねーんだ</t>
+          <t xml:space="preserve">この勢いで突っ走るぜ！</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7671,14 +7671,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふざけんなよ</t>
+          <t xml:space="preserve">…ここにいても、先が見えねえ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7703,14 +7703,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ガキが調子乗ってんじゃねーよ</t>
+          <t xml:space="preserve">…最近、何のために戦ってんのか分かんねーんだ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">G1.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7735,14 +7735,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい加減使えよ。腐るぞ</t>
+          <t xml:space="preserve">…ふざけんなよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">G2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7767,14 +7767,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ハッ、群れるのは趣味じゃねーんだよ</t>
+          <t xml:space="preserve">…ガキが調子乗ってんじゃねーよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.delinquent.bold[1]</t>
+          <t xml:space="preserve">G3.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7799,14 +7799,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ。…寂しいなんて言わねーけど</t>
+          <t xml:space="preserve">…いい加減使えよ。腐るぞ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">R2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ザマァ見ろ</t>
+          <t xml:space="preserve">…ハッ、群れるのは趣味じゃねーんだよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">R3.modal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7863,14 +7863,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…クソッ…！</t>
+          <t xml:space="preserve">…チッ。…寂しいなんて言わねーけど</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7880,29 +7880,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.delinquent.bold[1]</t>
+          <t xml:space="preserve">R4.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！この金で栄養つけてもっと強くなるぜ！</t>
+          <t xml:space="preserve">…ザマァ見ろ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7912,29 +7912,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.delinquent.bold[1]</t>
+          <t xml:space="preserve">R5.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！帰る頃には別人だ！</t>
+          <t xml:space="preserve">…クソッ…！</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.delinquent.bold[1]</t>
+          <t xml:space="preserve">bonus.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7959,14 +7959,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">アンタが信じてくれんなら、やってやるよ！</t>
+          <t xml:space="preserve">おっしゃ！この金で栄養つけてもっと強くなるぜ！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.delinquent.bold[1]</t>
+          <t xml:space="preserve">camp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7991,14 +7991,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まってられるかよ！次は絶対やってやる！</t>
+          <t xml:space="preserve">やってやるぜ！帰る頃には別人だ！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.delinquent.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -8023,14 +8023,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな。あそこは、あたしらの場所だっただろ</t>
+          <t xml:space="preserve">アンタが信じてくれんなら、やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.delinquent.bold[1]</t>
+          <t xml:space="preserve">encourage.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目されんの大歓迎！やってやるぜ！</t>
+          <t xml:space="preserve">止まってられるかよ！次は絶対やってやる！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.delinquent.bold[1]</t>
+          <t xml:space="preserve">faction_decree.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8087,14 +8087,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
+          <t xml:space="preserve">ふざけんな。あそこは、私らの場所だっただろ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.delinquent.bold[1]</t>
+          <t xml:space="preserve">media.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">充電してくる！戻ったら全開だぜ！</t>
+          <t xml:space="preserve">注目されんの大歓迎！やってやるぜ！</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.delinquent.bold[1]</t>
+          <t xml:space="preserve">party.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8151,14 +8151,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃあ！すぐ治して暴れに戻るぜ！</t>
+          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.delinquent.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8183,14 +8183,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高じゃん！限界まで追い込んでもらうぜ！</t>
+          <t xml:space="preserve">充電してくる！戻ったら全開だぜ！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.delinquent.bold[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！注目されんのは大歓迎だ！</t>
+          <t xml:space="preserve">しゃあ！すぐ治して暴れに戻るぜ！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.delinquent.bold[1]</t>
+          <t xml:space="preserve">trainer.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8247,14 +8247,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話来てんだよ。考えさせてくれ</t>
+          <t xml:space="preserve">最高じゃん！限界まで追い込んでもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.bold[1]</t>
+          <t xml:space="preserve">E1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8279,14 +8279,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ？やる気出ないっつの。文句あんなら試合組めよ</t>
+          <t xml:space="preserve">やってやるぜ！注目されんのは大歓迎だ！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.delinquent.bold[1]</t>
+          <t xml:space="preserve">E6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8311,14 +8311,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「なんであたしらがこんな扱い受けなきゃなんねぇんだよ」とロッカーで吠えている）</t>
+          <t xml:space="preserve">他所からいい話来てんだよ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.delinquent.bold[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8343,14 +8343,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わる気はねぇから」と宣戦布告じみた投稿）</t>
+          <t xml:space="preserve">はぁ？やる気出ないっつの。文句あんなら試合組めよ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.delinquent.bold[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトよこせ！今すぐ組め！</t>
+          <t xml:space="preserve">（「なんで私らがこんな扱い受けなきゃなんねぇんだよ」とロッカーで吠えている）</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.delinquent.bold[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8407,14 +8407,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつと決着つけさせろ！</t>
+          <t xml:space="preserve">（SNSに「このまま終わる気はねぇから」と宣戦布告じみた投稿）</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.delinquent.bold[1]</t>
+          <t xml:space="preserve">S1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8439,14 +8439,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がもう限界だ。休ませてくれ</t>
+          <t xml:space="preserve">ベルトよこせ！今すぐ組め！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.delinquent.bold[1]</t>
+          <t xml:space="preserve">S2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8471,14 +8471,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんじゃやってらんねーよ！改善しろ！</t>
+          <t xml:space="preserve">あいつと決着つけさせろ！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.delinquent.bold[1]</t>
+          <t xml:space="preserve">S3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8503,14 +8503,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（舌打ちをこらえて、拳を握っている）</t>
+          <t xml:space="preserve">くそ…体がもう限界だ。休ませてくれ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.delinquent.bold[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8535,14 +8535,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりてぇ！特訓させろ！</t>
+          <t xml:space="preserve">こんなんじゃやってらんねーよ！改善しろ！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.delinquent.bold[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8567,14 +8567,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒は任せろ。鍛えてやる</t>
+          <t xml:space="preserve">…………（舌打ちをこらえて、拳を握っている）</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.delinquent.bold[1]</t>
+          <t xml:space="preserve">S5.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8599,14 +8599,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…こんなとこで止まってらんねえ！</t>
+          <t xml:space="preserve">もっと強くなりてぇ！特訓させろ！</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.delinquent.bold[1]</t>
+          <t xml:space="preserve">S6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8631,14 +8631,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつの態度が気に食わねえ！限界だ！</t>
+          <t xml:space="preserve">後輩の面倒は任せろ。鍛えてやる</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.delinquent.bold[1]</t>
+          <t xml:space="preserve">B1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってると思うなよ！向こうが謝れ！</t>
+          <t xml:space="preserve">くそっ…こんなとこで止まってらんねえ！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.delinquent.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8695,14 +8695,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品、派手にやってやる！</t>
+          <t xml:space="preserve">あいつの態度が気に食わねえ！限界だ！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.delinquent.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8727,14 +8727,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？ 全国にこの顔を売りつけてやる！</t>
+          <t xml:space="preserve">黙ってると思うなよ！向こうが謝れ！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンイベ、盛り上げてやるよ！</t>
+          <t xml:space="preserve">コラボ商品、派手にやってやる！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8791,14 +8791,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">歩くだけなら怖くない。ど派手にやってやる</t>
+          <t xml:space="preserve">CM？ 全国にこの顔を売りつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_fan.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8823,14 +8823,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアも勝負事だ。全力でいくよ</t>
+          <t xml:space="preserve">ファンイベ、盛り上げてやるよ！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 絶対爪痕残す！</t>
+          <t xml:space="preserve">歩くだけなら怖くない。ど派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見せてやるぜ！かかってこい！</t>
+          <t xml:space="preserve">グラビアも勝負事だ。全力でいくよ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8904,29 +8904,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 絶対爪痕残す！</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8936,29 +8936,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
+          <t xml:space="preserve">全国に見せてやるぜ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8983,14 +8983,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
+          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
@@ -9015,14 +9015,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
+          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9047,14 +9047,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
+          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
@@ -9079,14 +9079,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
+          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9111,14 +9111,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
+          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9143,14 +9143,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう決着はついてんだよ。何度潰されりゃ気が済む</t>
+          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9175,14 +9175,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの日から一度も、まともに寝てねえんだよ</t>
+          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.delinquent.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9207,14 +9207,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
+          <t xml:space="preserve">もう決着はついてんだよ。何度潰されりゃ気が済む</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9239,14 +9239,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
+          <t xml:space="preserve">あの日から一度も、まともに寝てねえんだよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.bold[2]</t>
+          <t xml:space="preserve">draftInterest.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9271,14 +9271,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
+          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9303,14 +9303,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.delinquent.bold[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9335,14 +9335,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
+          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.delinquent.bold[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9367,14 +9367,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
+          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.delinquent.bold[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9399,14 +9399,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
+          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.delinquent.bold[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9431,14 +9431,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
+          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.delinquent.bold[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9463,14 +9463,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
+          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.bold[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9495,14 +9495,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
+          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.bold[2]</t>
+          <t xml:space="preserve">heatSelf.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9527,14 +9527,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
+          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.bold[1]</t>
+          <t xml:space="preserve">injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9559,14 +9559,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
+          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.bold[2]</t>
+          <t xml:space="preserve">injury.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9591,14 +9591,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
+          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9623,14 +9623,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
+          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">release.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9655,14 +9655,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
+          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9687,14 +9687,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
+          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.delinquent.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9719,14 +9719,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
+          <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9751,14 +9751,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
+          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
+          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9815,14 +9815,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
+          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">titleWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9847,14 +9847,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
+          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
@@ -9879,14 +9879,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
+          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9911,14 +9911,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
+          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
@@ -9943,14 +9943,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
+          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9975,14 +9975,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
+          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
@@ -10007,14 +10007,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
+          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10024,29 +10024,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">虫が好かねぇんだよ</t>
+          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10056,29 +10056,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近態度おかしくね？ ムカつくな</t>
+          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10103,14 +10103,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込みあるよ。面倒見てやるか</t>
+          <t xml:space="preserve">虫が好かねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.delinquent[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10135,14 +10135,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フン、気に入ったぜ</t>
+          <t xml:space="preserve">おい、最近態度おかしくね？ ムカつくな</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10167,14 +10167,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒だ。文句あるか</t>
+          <t xml:space="preserve">見込みあるよ。面倒見てやるか</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.delinquent[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10199,14 +10199,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時代は終わりだ。もう眼中にねぇ</t>
+          <t xml:space="preserve">フン、気に入ったぜ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10231,14 +10231,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面ぁ見ると血が騒ぐんだよ</t>
+          <t xml:space="preserve">相棒だ。文句あるか</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10263,14 +10263,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">這いつくばらせてやる…！</t>
+          <t xml:space="preserve">時代は終わりだ。もう眼中にねぇ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10295,14 +10295,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">生涯の敵だ。最後まで殴り合ってやる</t>
+          <t xml:space="preserve">面ぁ見ると血が騒ぐんだよ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10327,14 +10327,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは最高だ。あたしがてっぺんまで連れてってやるよ</t>
+          <t xml:space="preserve">這いつくばらせてやる…！</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10359,14 +10359,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしを舐めてんなら出てってやるよ。後悔するなよ</t>
+          <t xml:space="preserve">生涯の敵だ。最後まで殴り合ってやる</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10391,14 +10391,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なめんじゃねぇぞ。あたしをもっと使え</t>
+          <t xml:space="preserve">ここは最高だ。私がてっぺんまで連れてってやるよ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.delinquent.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10423,14 +10423,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次会ったらぶっ飛ばしてやる…覚えてろ</t>
+          <t xml:space="preserve">私を舐めてんなら出てってやるよ。後悔するなよ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.delinquent.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10455,14 +10455,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へっ、雑魚が。話にならねぇ</t>
+          <t xml:space="preserve">なめんじゃねぇぞ。私をもっと使え</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-01.loss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10487,14 +10487,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おらおら、休んでる暇ねぇぞ！</t>
+          <t xml:space="preserve">次会ったらぶっ飛ばしてやる…覚えてろ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-01.win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10519,14 +10519,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダチだ。大事にしてやるよ</t>
+          <t xml:space="preserve">へっ、雑魚が。話にならねぇ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10551,14 +10551,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えるまで止まらねぇ</t>
+          <t xml:space="preserve">おらおら、休んでる暇ねぇぞ！</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10583,14 +10583,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おいこら！ あたしを出せよ！ 暴れたいんだよ！</t>
+          <t xml:space="preserve">ダチだ。大事にしてやるよ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10615,14 +10615,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ、こんな体じゃ戦えねぇだろ…！</t>
+          <t xml:space="preserve">超えるまで止まらねぇ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-06.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10647,14 +10647,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…いつまで負けてんだよ…！</t>
+          <t xml:space="preserve">おいこら！ 私を出せよ！ 暴れたいんだよ！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-07.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10679,14 +10679,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まらねぇぜ！ 全員ぶっ倒す！</t>
+          <t xml:space="preserve">くそっ、こんな体じゃ戦えねぇだろ…！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10711,14 +10711,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ…じっとしてらんねぇ。もう走れるだろ…！</t>
+          <t xml:space="preserve">ふざけんな…いつまで負けてんだよ…！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-09.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10743,14 +10743,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子戻っちまったけど、あの感覚は覚えたぜ</t>
+          <t xml:space="preserve">止まらねぇぜ！ 全員ぶっ倒す！</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10760,29 +10760,29 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-10.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体? 知るかよ。最後まで残ったんだ、テッペン獲るに決まってんだろ</t>
+          <t xml:space="preserve">チッ…じっとしてらんねぇ。もう走れるだろ…！</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10792,29 +10792,29 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボロボロだろうが関係ねえ。この一戦、ぶっ潰して終わらせる</t>
+          <t xml:space="preserve">調子戻っちまったけど、あの感覚は覚えたぜ</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[3]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10839,14 +10839,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛え? あたりめえだろ。でもここで倒れたら、今までが無駄になる。行くぞ</t>
+          <t xml:space="preserve">身体？ 知るかよ。最後まで残ったんだ、テッペン獲るに決まってんだろ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10871,14 +10871,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ! 何人来ようがまとめてかかってこいや</t>
+          <t xml:space="preserve">ボロボロだろうが関係ねえ。この一戦、ぶっ潰して終わらせる</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10903,14 +10903,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつしか来れねえのか? じれってえな。全員まとめて潰してやる</t>
+          <t xml:space="preserve">痛え？ あたりめえだろ。でもここで倒れたら、今までが無駄になる。行くぞ</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[3]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10935,14 +10935,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、渡すわけねえだろ。出てこいよ、順番に沈めてやる</t>
+          <t xml:space="preserve">相手は誰だ！ 何人来ようがまとめてかかってこいや</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.bold[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10967,14 +10967,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒した! …はぁ、まだいけるぞ。次、どいつだ、出てこい!</t>
+          <t xml:space="preserve">一人ずつしか来れねえのか？ じれってえな。全員まとめて潰してやる</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.bold[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10999,14 +10999,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえ! このリング、渡すかよ。次、さっさとかかってこい!</t>
+          <t xml:space="preserve">このリング、渡すわけねえだろ。出てこいよ、順番に沈めてやる</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.bold[3]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11031,14 +11031,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人沈めたぞ! …はぁ、はぁ…まだ足りねえ。次、誰でもいい、来い!</t>
+          <t xml:space="preserve">一人ぶっ倒した！ …はぁ、まだいけるぞ。次、どいつだ、出てこい！</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11063,14 +11063,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしらが最強だ。文句あんなら、かかってこいよ</t>
+          <t xml:space="preserve">まだ終わってねえ！ このリング、渡すかよ。次、さっさとかかってこい！</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11095,14 +11095,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人揃って無敵だったな。最高のチームだぜ</t>
+          <t xml:space="preserve">一人沈めたぞ！ …はぁ、はぁ…まだ足りねえ。次、誰でもいい、来い！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.bold[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11127,14 +11127,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ はっ、こんなもんじゃ足りねえよ。次は丸ごとぶん取る</t>
+          <t xml:space="preserve">私らが最強だ。文句あんなら、かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.bold[2]</t>
+          <t xml:space="preserve">champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11159,14 +11159,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっとくけど、次は優勝旗ごと叩き取る。覚えとけ</t>
+          <t xml:space="preserve">三人揃って無敵だったな。最高のチームだぜ</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.bold[1]</t>
+          <t xml:space="preserve">defiant.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11191,14 +11191,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るだけ来いっつったろ？ 全員ぶっ倒して、まだ余裕あんぞ</t>
+          <t xml:space="preserve">MVP？ はっ、こんなもんじゃ足りねえよ。次は丸ごとぶん取る</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.bold[2]</t>
+          <t xml:space="preserve">defiant.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11223,14 +11223,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人並ぼうが一緒だ。あたしの前に立つなら覚悟しろ</t>
+          <t xml:space="preserve">賞はもらっとくけど、次は優勝旗ごと叩き取る。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11255,14 +11255,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったろ？ テッペンは俺のもんだってな</t>
+          <t xml:space="preserve">来るだけ来いっつったろ？ 全員ぶっ倒して、まだ余裕あんぞ</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、当然の結果だぜ。誰にも負けねえ</t>
+          <t xml:space="preserve">何人並ぼうが一緒だ。私の前に立つなら覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.bold[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11319,14 +11319,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…！ 次は絶対ぶっ潰す！</t>
+          <t xml:space="preserve">言ったろ？ テッペンは私のもんだってな</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.bold[2]</t>
+          <t xml:space="preserve">champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11351,14 +11351,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなん認めねえ…！</t>
+          <t xml:space="preserve">はっ、当然の結果だぜ。誰にも負けねえ</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">postLose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11383,14 +11383,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、楽勝だぜ。次も同じだ</t>
+          <t xml:space="preserve">ふざけんな…！ 次は絶対ぶっ潰す！</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">postLose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11415,14 +11415,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止められるもんなら止めてみろ</t>
+          <t xml:space="preserve">こんなん認めねえ…！</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11447,14 +11447,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ、まだ足りねえ。次は全員ぶっ倒す</t>
+          <t xml:space="preserve">はっ、楽勝だぜ。次も同じだ</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11479,14 +11479,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ上がいるってのがムカつくぜ</t>
+          <t xml:space="preserve">止められるもんなら止めてみろ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">postWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11511,14 +11511,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たからにゃ、テッペン獲るに決まってんだろ</t>
+          <t xml:space="preserve">ちっ、まだ足りねえ。次は全員ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">postWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11543,14 +11543,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の相手か。ぶっ壊してやるよ</t>
+          <t xml:space="preserve">まだ上がいるってのがムカつくぜ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11575,14 +11575,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">邪魔するヤツは全員ぶっ倒す</t>
+          <t xml:space="preserve">ここまで来たからにゃ、テッペン獲るに決まってんだろ</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11607,14 +11607,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かかって来いよ。一発で沈めてやる</t>
+          <t xml:space="preserve">最後の相手か。ぶっ壊してやるよ</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.bold[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11639,14 +11639,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あァ？ まあいいけど。暴れる場所が増えるだけだ</t>
+          <t xml:space="preserve">邪魔するヤツは全員ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.bold[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11671,14 +11671,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっせーな、勝手に呼びやがって。……まあ出るけど</t>
+          <t xml:space="preserve">かかって来いよ。一発で沈めてやる</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">summon.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11703,14 +11703,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰してやるぜ！泣いても知らねーぞ！</t>
+          <t xml:space="preserve">あァ？ まあいいけど。暴れる場所が増えるだけだ</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">summon.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11735,14 +11735,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぞ……！ 全員ぶっ倒してここまで来たんだ……！</t>
+          <t xml:space="preserve">うっせーな、勝手に呼びやがって。……まあ出るけど</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
@@ -11767,14 +11767,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てめえらの団体？ うちの新人にも勝てねえだろ</t>
+          <t xml:space="preserve">ぶっ潰してやるぜ！泣いても知らねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11799,14 +11799,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰してやるよ。覚悟しろ</t>
+          <t xml:space="preserve">やったぞ……！ 全員ぶっ倒してここまで来たんだ……！</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
@@ -11831,14 +11831,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、ザッコ。逃げんのかよ</t>
+          <t xml:space="preserve">てめえらの団体？ うちの新人にも勝てねえだろ</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
@@ -11863,14 +11863,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次会った時は逃がさねえからな。覚えとけ</t>
+          <t xml:space="preserve">ぶっ潰してやるよ。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…マジかよ…。絶対リベンジしてやる</t>
+          <t xml:space="preserve">はっ、ザッコ。逃げんのかよ</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11927,14 +11927,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…次はぶっ壊してやるからな</t>
+          <t xml:space="preserve">次会った時は逃がさねえからな。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.bold[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11959,14 +11959,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、楽勝だぜ。雑魚が調子乗んなよ</t>
+          <t xml:space="preserve">ちっ…マジかよ…。絶対リベンジしてやる</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.bold[2]</t>
+          <t xml:space="preserve">result_lose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11991,14 +11991,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがウチの強さだ。分かったか</t>
+          <t xml:space="preserve">ふざけんな…次はぶっ壊してやるからな</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">result_win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -12023,14 +12023,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然だろ！ うちの団体なめんじゃねえよ！</t>
+          <t xml:space="preserve">はっ、楽勝だぜ。雑魚が調子乗んなよ</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">result_win.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12055,14 +12055,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ざまあみろ！ これがうちの実力だ！</t>
+          <t xml:space="preserve">これがウチの強さだ。分かったか</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[3]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12087,14 +12087,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体に手ぇ出すからだ。ざまぁみろ</t>
+          <t xml:space="preserve">当然だろ！ うちの団体なめんじゃねえよ！</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12104,29 +12104,29 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲ったぜ！でもまだまだこれからだ！</t>
+          <t xml:space="preserve">ざまあみろ！ これがうちの実力だ！</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12136,59 +12136,123 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+          <t xml:space="preserve">うちの団体に手ぇ出すからだ。ざまぁみろ</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">てっぺん獲ったぜ！でもまだまだこれからだ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="40" customHeight="1">
+      <c r="A368" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="40" customHeight="1">
+      <c r="A369" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr" s="2">
+      <c r="B369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr" s="12">
+      <c r="D369" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr" s="2">
+      <c r="E369" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr" s="3">
+      <c r="F369" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H367"/>
+  <autoFilter ref="A1:H369"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
@@ -7095,7 +7095,7 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦の頂点はあたしたちだ。異論あるならまた来な。</t>
+          <t xml:space="preserve">対抗戦の頂点は私らだ。異論あるならまた来な。</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ただろ。あたしたちのタッグが一番強いんだよ。</t>
+          <t xml:space="preserve">見ただろ。私らのタッグが一番強いんだよ。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H369"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4026,7 +4026,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.delinquent.bold[1]</t>
+          <t xml:space="preserve">decline_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -4051,14 +4051,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ま、当然だけどな。ちゃんと評価してくれんじゃん。</t>
+          <t xml:space="preserve">上等。それが今の私の値段ってことね。……安く買ったって、後悔させてやる。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.delinquent.bold[1]</t>
+          <t xml:space="preserve">decline_hold.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4083,14 +4083,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ま、ゼロよりマシか。次はもっと出せよな。</t>
+          <t xml:space="preserve">据え置き？ ……施しは受けない主義なんだけどね。……ま、借りにしとくよ。倍にして返す。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.delinquent.bold[1]</t>
+          <t xml:space="preserve">decline_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……は？ マジかよ。……まあいい。でも次はねーぞ。</t>
+          <t xml:space="preserve">下げる、ね。……止めやしないよ。ただ、この数字が私の底だと思ってんなら、その目は節穴。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.delinquent.bold[1]</t>
+          <t xml:space="preserve">decline_strict.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4147,14 +4147,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい社長。{tenure}この給料はふざけてんのか。{record}ちゃんと評価しろよ。</t>
+          <t xml:space="preserve">……へえ。ボーナスまで。……分かった。それがあんたのやり方なら、私は私のやり方でいく。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.delinquent.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4179,14 +4179,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……は？ ……ふーん。まあいいけどよ、限界ってもんがあるからな。</t>
+          <t xml:space="preserve">話が早くて助かる。言っとくけど、下がったのは値段だけだから。中身は勝手に上げていく。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.delinquent.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4211,14 +4211,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あーもう無理。やってらんない。辞めるわ。</t>
+          <t xml:space="preserve">……人の話、聞いてた？ ……ふん。……その額に私が追いつくまで、辞められなくなったじゃん。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.bold[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.delinquent.bold[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">金も信頼もないんじゃ、いる意味ないっしょ。バイバイ。</t>
+          <t xml:space="preserve">先に言うよ。今の私に、前と同じ額は釣り合わない。……下げな。もらいすぎってのは、性に合わない。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.delinquent.bold[1]</t>
+          <t xml:space="preserve">raise_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4275,14 +4275,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれんのか。{record}正直、もっと上で闘いてーんだよ。物足りねー。</t>
+          <t xml:space="preserve">……ま、当然だけどな。ちゃんと評価してくれんじゃん。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.delinquent.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}もう決めた。ここ出るぜ。</t>
+          <t xml:space="preserve">……ま、ゼロよりマシか。次はもっと出せよな。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.delinquent.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……だろうな。分かってたぜ。{rivalry}じゃーな、社長。</t>
+          <t xml:space="preserve">……は？ マジかよ。……まあいい。でも次はねーぞ。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.delinquent.bold[1]</t>
+          <t xml:space="preserve">raise_open.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いけど、もう決めた。何言われても変わらねー。</t>
+          <t xml:space="preserve">おい社長。{tenure}この給料はふざけてんのか。{record}ちゃんと評価しろよ。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.delinquent.bold[1]</t>
+          <t xml:space="preserve">raise_refuse.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4403,370 +4403,370 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……チッ。そこまで言うなら、もうちょい付き合ってやるよ。</t>
+          <t xml:space="preserve">……は？ ……ふーん。まあいいけどよ、限界ってもんがあるからな。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あーもう無理。やってらんない。辞めるわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.bold[2]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.delinquent.bold[2]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">金も信頼もないんじゃ、いる意味ないっしょ。バイバイ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……聞いてくれんのか。{record}正直、もっと上で闘いてーんだよ。物足りねー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}もう決めた。ここ出るぜ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……だろうな。分かってたぜ。{rivalry}じゃーな、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪いけど、もう決めた。何言われても変わらねー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……チッ。そこまで言うなら、もうちょい付き合ってやるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私が今の仲間に背くと思ったか？
 甘ぇよ、帰れ</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここが私の居場所だ。
 出直してきな</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私を引き抜く？
 面白ぇ度胸してんじゃねーか</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認めてやるぜ。
 新しい場所で格の違い見せてやらぁ！</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私らのこと、もうちょい大事にしてくんないっすか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメイン、私らでいきますよ。話、通してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私らの給料、見直してくれません？ はっきり言って足りないっす。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私らの働き、ちゃんと数えてんですか。はっきり言ってもらえます？</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとうございます社長。その一言で十分っすよ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…っす。失礼しました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.delinquent.bold[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…っす、そういう形なら、ありがたく頂戴します。</t>
-        </is>
-      </c>
-    </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。客、ぶち上げてみせますよ。</t>
+          <t xml:space="preserve">社長、私らのこと、もうちょい大事にしてくんないっすか。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4823,14 +4823,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす。わかりました。</t>
+          <t xml:space="preserve">社長、次のメイン、私らでいきますよ。話、通してください。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4855,14 +4855,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす。まあ、そういう形ならありがたく。</t>
+          <t xml:space="preserve">社長、私らの給料、見直してくれません？ はっきり言って足りないっす。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4887,14 +4887,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか、社長ありがとうございます！ みんな喜びますよ。</t>
+          <t xml:space="preserve">社長、私らの働き、ちゃんと数えてんですか。はっきり言ってもらえます？</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4919,14 +4919,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす。わかりました。</t>
+          <t xml:space="preserve">ありがとうございます社長。その一言で十分っすよ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4951,14 +4951,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす。お金じゃないけど、まあありがたいっす。</t>
+          <t xml:space="preserve">…っす。失礼しました。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あんがとっす。そう言われちゃ、気合い入るっすよ。</t>
+          <t xml:space="preserve">…っす、そういう形なら、ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -5015,14 +5015,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす。失礼しました。</t>
+          <t xml:space="preserve">ありがとうございます。客、ぶち上げてみせますよ。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、そういう形なら、ありがたく頂戴します。</t>
+          <t xml:space="preserve">…っす。わかりました。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5079,14 +5079,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。次は声かけます。</t>
+          <t xml:space="preserve">…っす。まあ、そういう形ならありがたく。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。仲間内の付き合いも大事っすから。</t>
+          <t xml:space="preserve">マジっすか、社長ありがとうございます！ みんな喜びますよ。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5143,14 +5143,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。気をつけます。</t>
+          <t xml:space="preserve">…っす。わかりました。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5175,14 +5175,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。</t>
+          <t xml:space="preserve">…っす。お金じゃないけど、まあありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。営業に響くなら線引きます。</t>
+          <t xml:space="preserve">社長、あんがとっす。そう言われちゃ、気合い入るっすよ。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5239,14 +5239,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。これも仕事のうちっす。</t>
+          <t xml:space="preserve">…っす。失礼しました。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5271,14 +5271,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、すんません。明日からちゃんと出ます。</t>
+          <t xml:space="preserve">…っす、そういう形なら、ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5303,14 +5303,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。</t>
+          <t xml:space="preserve">…っす、わかりました。次は声かけます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5335,14 +5335,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、メンバー優先っすか。ありがたいっす。</t>
+          <t xml:space="preserve">…っす、ありがとうございます。仲間内の付き合いも大事っすから。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5367,14 +5367,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。ちょっと休みます。</t>
+          <t xml:space="preserve">…っす、わかりました。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5399,14 +5399,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、大丈夫っす。問題ないっす。</t>
+          <t xml:space="preserve">…っす、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、メンバーケアっすか。助かります。</t>
+          <t xml:space="preserve">…っす、わかりました。営業に響くなら線引きます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5463,14 +5463,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。私から言っときます。</t>
+          <t xml:space="preserve">…っす、ありがとうございます。これも仕事のうちっす。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5495,14 +5495,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。</t>
+          <t xml:space="preserve">…っす、すんません。明日からちゃんと出ます。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5527,14 +5527,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、配慮ありがとうございます。下の子助かります。</t>
+          <t xml:space="preserve">…っす、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5559,14 +5559,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。気をつけます。</t>
+          <t xml:space="preserve">…っす、メンバー優先っすか。ありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5591,14 +5591,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（チッ、と舌打ちして、目を逸らした）</t>
+          <t xml:space="preserve">…っす、ありがとうございます。ちょっと休みます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5623,14 +5623,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、配慮ありがとうございます。</t>
+          <t xml:space="preserve">…っす、大丈夫っす。問題ないっす。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5655,14 +5655,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、わかりました。怪我さしたら意味ないっすね。緩めます。</t>
+          <t xml:space="preserve">…っす、メンバーケアっすか。助かります。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5687,14 +5687,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、ありがとうございます。このままいきます。</t>
+          <t xml:space="preserve">…っす、わかりました。私から言っときます。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っす、子たち優先っすか。ありがたいっす。</t>
+          <t xml:space="preserve">…っす、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.delinquent</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5736,12 +5736,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.delinquent</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、一緒にゃいられねえ</t>
+          <t xml:space="preserve">…っす、配慮ありがとうございます。下の子助かります。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.delinquent</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.delinquent</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5783,29 +5783,29 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等だ、かかってこい</t>
+          <t xml:space="preserve">…っす、わかりました。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5815,29 +5815,29 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めてんじゃねーぞって話だよ。毎回毎回、同じパターンで。</t>
+          <t xml:space="preserve">（チッ、と舌打ちして、目を逸らした）</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5847,29 +5847,29 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ったく、気まずいっての。</t>
+          <t xml:space="preserve">…っす、配慮ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5879,29 +5879,29 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等じゃねーか。来いよ、いつでも。</t>
+          <t xml:space="preserve">…っす、わかりました。怪我さしたら意味ないっすね。緩めます。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.hp_high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5911,29 +5911,29 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……負けた。今日のとこはな</t>
+          <t xml:space="preserve">…っす、ありがとうございます。このままいきます。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_low[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.hp_low[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5943,29 +5943,29 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（息も荒い）</t>
+          <t xml:space="preserve">…っす、子たち優先っすか。ありがたいっす。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_mid[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.delinquent</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.hp_mid[1]</t>
+          <t xml:space="preserve">bold.attack.delinquent</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5975,29 +5975,29 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うるせえ……</t>
+          <t xml:space="preserve">もう、一緒にゃいられねえ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.delinquent</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[1]</t>
+          <t xml:space="preserve">bold.defend.delinquent</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -6007,14 +6007,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">口ほどにもねえな、あんたの組</t>
+          <t xml:space="preserve">上等だ、かかってこい</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.high[2]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -6039,14 +6039,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の番、誰だよ？　全員かかってこい</t>
+          <t xml:space="preserve">舐めてんじゃねーぞって話だよ。毎回毎回、同じパターンで。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.mid[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.mid[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6071,14 +6071,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん。私の勝ちだ</t>
+          <t xml:space="preserve">……ったく、気まずいっての。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6103,14 +6103,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜、あんたの組は終わる。しっかり見とけよ</t>
+          <t xml:space="preserve">上等じゃねーか。来いよ、いつでも。</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_high[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[2]</t>
+          <t xml:space="preserve">delinquent.bold.hp_high[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ヘラヘラしてられんのも今のうちだぜ</t>
+          <t xml:space="preserve">チッ……負けた。今日のとこはな</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[3]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_low[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[3]</t>
+          <t xml:space="preserve">delinquent.bold.hp_low[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6167,14 +6167,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めた口きいてた連中、ぜんぶ纏めて私が叩く</t>
+          <t xml:space="preserve">（息も荒い）</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.delinquent.bold.hp_mid[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.mid[1]</t>
+          <t xml:space="preserve">delinquent.bold.hp_mid[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6199,14 +6199,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙って来な。話すことなんかねえだろ</t>
+          <t xml:space="preserve">……うるせえ……</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、待ってたぞ。逃がさねえからな</t>
+          <t xml:space="preserve">口ほどにもねえな、あんたの組</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしんとこも、舐められたまま終わる気はねえ</t>
+          <t xml:space="preserve">次の番、誰だよ？　全員かかってこい</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
@@ -6295,14 +6295,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ったく。来るなら来いよ</t>
+          <t xml:space="preserve">ふん。私の勝ちだ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
@@ -6327,14 +6327,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完全勝利だ。文句あるか？</t>
+          <t xml:space="preserve">今夜、あんたの組は終わる。しっかり見とけよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6359,14 +6359,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次。次出てこい</t>
+          <t xml:space="preserve">ヘラヘラしてられんのも今のうちだぜ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.high[3]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[3]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6391,14 +6391,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員揃ってるな？ じゃあ、今夜が最後だ</t>
+          <t xml:space="preserve">舐めた口きいてた連中、ぜんぶ纏めて私が叩く</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold.high[1]</t>
+          <t xml:space="preserve">delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来なよ。全員でかかってこい</t>
+          <t xml:space="preserve">黙って来な。話すことなんかねえだろ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.delinquent.bold.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
@@ -6455,14 +6455,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙って退け、なんて言わねえ。リングで証明してやる</t>
+          <t xml:space="preserve">おう、待ってたぞ。逃がさねえからな</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.delinquent.bold.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
@@ -6487,238 +6487,238 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が上に立つ。それだけだ</t>
+          <t xml:space="preserve">わたしんとこも、舐められたまま終わる気はねえ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.mid[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然だろ！ まだまだこんなもんじゃねーぜ！</t>
+          <t xml:space="preserve">ったく。来るなら来いよ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…体が勝手に動きやがる。これが限界の先かよ——）</t>
+          <t xml:space="preserve">完全勝利だ。文句あるか？</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.delinquent.bold[1]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
+          <t xml:space="preserve">次。次出てこい</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.delinquent.bold[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
+          <t xml:space="preserve">全員揃ってるな？ じゃあ、今夜が最後だ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.delinquent.bold[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
+          <t xml:space="preserve">来なよ。全員でかかってこい</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.bold[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">クソ、ここが限界かよ…でも、まだ他で勝負できる</t>
+          <t xml:space="preserve">黙って退け、なんて言わねえ。リングで証明してやる</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.bold[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold.high[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見えてきたぜ、てっぺんが！</t>
+          <t xml:space="preserve">私が上に立つ。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.bold[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6743,14 +6743,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからだっつーの！ まだ全然足りねえ</t>
+          <t xml:space="preserve">当然だろ！ まだまだこんなもんじゃねーぜ！</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.bold[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6775,14 +6775,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんだ！ 文句あるやつは掛かってこい！</t>
+          <t xml:space="preserve">（…体が勝手に動きやがる。これが限界の先かよ——）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.delinquent.bold[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.delinquent.bold[1]</t>
+          <t xml:space="preserve">fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6807,14 +6807,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと気づいたか！ もっと見とけよ！</t>
+          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.bold[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.delinquent.bold[1]</t>
+          <t xml:space="preserve">heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6839,14 +6839,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめて最高の試合見せてやるぜ！</t>
+          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6871,14 +6871,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えねーんだよ。何やっても、火がつかねー</t>
+          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">cap_reached.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6903,14 +6903,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目ぇ覚めたぜ。ここで終わるかよ</t>
+          <t xml:space="preserve">クソ、ここが限界かよ…でも、まだ他で勝負できる</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">ovr_elite.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6935,14 +6935,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待たせたな！ ここからだぜ！</t>
+          <t xml:space="preserve">見えてきたぜ、てっぺんが！</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.delinquent.bold[1]</t>
+          <t xml:space="preserve">ovr_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6967,14 +6967,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ、何やってんだよ私</t>
+          <t xml:space="preserve">ここからだっつーの！ まだ全然足りねえ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.delinquent.bold[1]</t>
+          <t xml:space="preserve">ovr_legend.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6999,14 +6999,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">治ったっつーのに…何でもたついてんだ</t>
+          <t xml:space="preserve">てっぺんだ！ 文句あるやつは掛かってこい！</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.delinquent.bold[1]</t>
+          <t xml:space="preserve">pop_growth.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7031,14 +7031,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がビビってる？ ふざけんな</t>
+          <t xml:space="preserve">やっと気づいたか！ もっと見とけよ！</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.delinquent.bold[1]</t>
+          <t xml:space="preserve">pop_star.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7063,14 +7063,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全なのに…気持ちがついてこねー</t>
+          <t xml:space="preserve">全員まとめて最高の試合見せてやるぜ！</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7080,29 +7080,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対抗戦の頂点は私らだ。異論あるならまた来な。</t>
+          <t xml:space="preserve">…燃えねーんだよ。何やっても、火がつかねー</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7112,29 +7112,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殴って殴られて、最後に立ってた。それだけだ。…最高だったけどな</t>
+          <t xml:space="preserve">目ぇ覚めたぜ。ここで終わるかよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7144,29 +7144,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強は私だ。証拠がここにある。文句は拳で言いに来い</t>
+          <t xml:space="preserve">待たせたな！ ここからだぜ！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7176,29 +7176,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.delinquent.bold[1]</t>
+          <t xml:space="preserve">defeat.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりたい放題やって、全部勝ち取った。最高の人生だ</t>
+          <t xml:space="preserve">…チッ、何やってんだよ私</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7208,29 +7208,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.delinquent.bold[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃ！ 来年はもっとやったるぞ！</t>
+          <t xml:space="preserve">治ったっつーのに…何でもたついてんだ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7240,29 +7240,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.delinquent.bold[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一番強かったのは私だ。文句あるなら来いよ</t>
+          <t xml:space="preserve">私がビビってる？ ふざけんな</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7272,29 +7272,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.delinquent.bold[1]</t>
+          <t xml:space="preserve">penalty_end.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ハッ、新人なのは今年だけだ。来年は全部かっさらう</t>
+          <t xml:space="preserve">体は万全なのに…気持ちがついてこねー</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.delinquent.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7319,14 +7319,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見ただろ。私らのタッグが一番強いんだよ。</t>
+          <t xml:space="preserve">対抗戦の頂点は私らだ。異論あるならまた来な。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7351,14 +7351,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おうっ、ドームだろうが関係ねえ。ぶっ壊すだけだ</t>
+          <t xml:space="preserve">殴って殴られて、最後に立ってた。それだけだ。…最高だったけどな</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7383,14 +7383,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最後じゃねえ。まだ先、あるからな</t>
+          <t xml:space="preserve">最強は私だ。証拠がここにある。文句は拳で言いに来い</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[3]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7415,14 +7415,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員ひっくり返してやる。見てろよ</t>
+          <t xml:space="preserve">やりたい放題やって、全部勝ち取った。最高の人生だ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">mediaAward.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7447,14 +7447,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員、ひっくり返せた気がすんな。満員にしやがって</t>
+          <t xml:space="preserve">よっしゃ！ 来年はもっとやったるぞ！</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">mvp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7479,14 +7479,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそおおお、やってやったぜドーム満員！！</t>
+          <t xml:space="preserve">一番強かったのは私だ。文句あるなら来いよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[3]</t>
+          <t xml:space="preserve">rookie.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7511,14 +7511,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚えとけよ、観客全員。またぶっ壊しに来るからな</t>
+          <t xml:space="preserve">ハッ、新人なのは今年だけだ。来年は全部かっさらう</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7528,29 +7528,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.bold[1]</t>
+          <t xml:space="preserve">springTagChampion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りねえ。もっとやれるはずだ</t>
+          <t xml:space="preserve">見ただろ。私らのタッグが一番強いんだよ。</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7560,29 +7560,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつがいるから燃えるんだよ！</t>
+          <t xml:space="preserve">おうっ、ドームだろうが関係ねえ。ぶっ壊すだけだ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7592,29 +7592,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で止まってられるかよ</t>
+          <t xml:space="preserve">ここが最後じゃねえ。まだ先、あるからな</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7624,29 +7624,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢いで突っ走るぜ！</t>
+          <t xml:space="preserve">…全員ひっくり返してやる。見てろよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7656,29 +7656,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいても、先が見えねえ</t>
+          <t xml:space="preserve">…全員、ひっくり返せた気がすんな。満員にしやがって</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7688,29 +7688,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近、何のために戦ってんのか分かんねーんだ</t>
+          <t xml:space="preserve">くっそおおお、やってやったぜドーム満員！！</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふざけんなよ</t>
+          <t xml:space="preserve">…覚えとけよ、観客全員。またぶっ壊しに来るからな</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7767,14 +7767,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ガキが調子乗ってんじゃねーよ</t>
+          <t xml:space="preserve">まだ足りねえ。もっとやれるはずだ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7799,14 +7799,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい加減使えよ。腐るぞ</t>
+          <t xml:space="preserve">あいつがいるから燃えるんだよ！</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ハッ、群れるのは趣味じゃねーんだよ</t>
+          <t xml:space="preserve">この程度で止まってられるかよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.delinquent.bold[1]</t>
+          <t xml:space="preserve">N4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7863,14 +7863,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ。…寂しいなんて言わねーけど</t>
+          <t xml:space="preserve">この勢いで突っ走るぜ！</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7895,14 +7895,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ザマァ見ろ</t>
+          <t xml:space="preserve">…ここにいても、先が見えねえ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.delinquent.bold[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7927,14 +7927,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…クソッ…！</t>
+          <t xml:space="preserve">…最近、何のために戦ってんのか分かんねーんだ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7944,29 +7944,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.delinquent.bold[1]</t>
+          <t xml:space="preserve">G1.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ！この金で栄養つけてもっと強くなるぜ！</t>
+          <t xml:space="preserve">…ふざけんなよ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7976,29 +7976,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.delinquent.bold[1]</t>
+          <t xml:space="preserve">G2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！帰る頃には別人だ！</t>
+          <t xml:space="preserve">…ガキが調子乗ってんじゃねーよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -8008,29 +8008,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.delinquent.bold[1]</t>
+          <t xml:space="preserve">G3.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">アンタが信じてくれんなら、やってやるよ！</t>
+          <t xml:space="preserve">…いい加減使えよ。腐るぞ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8040,29 +8040,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.delinquent.bold[1]</t>
+          <t xml:space="preserve">R2.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まってられるかよ！次は絶対やってやる！</t>
+          <t xml:space="preserve">…ハッ、群れるのは趣味じゃねーんだよ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8072,29 +8072,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.delinquent.bold[1]</t>
+          <t xml:space="preserve">R3.modal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな。あそこは、私らの場所だっただろ</t>
+          <t xml:space="preserve">…チッ。…寂しいなんて言わねーけど</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8104,29 +8104,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.delinquent.bold[1]</t>
+          <t xml:space="preserve">R4.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目されんの大歓迎！やってやるぜ！</t>
+          <t xml:space="preserve">…ザマァ見ろ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8136,29 +8136,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.delinquent.bold[1]</t>
+          <t xml:space="preserve">R5.voice.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
+          <t xml:space="preserve">…クソッ…！</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.delinquent.bold[1]</t>
+          <t xml:space="preserve">bonus.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8183,14 +8183,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">充電してくる！戻ったら全開だぜ！</t>
+          <t xml:space="preserve">おっしゃ！この金で栄養つけてもっと強くなるぜ！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.delinquent.bold[1]</t>
+          <t xml:space="preserve">camp.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しゃあ！すぐ治して暴れに戻るぜ！</t>
+          <t xml:space="preserve">やってやるぜ！帰る頃には別人だ！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.delinquent.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8247,14 +8247,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高じゃん！限界まで追い込んでもらうぜ！</t>
+          <t xml:space="preserve">アンタが信じてくれんなら、やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.delinquent.bold[1]</t>
+          <t xml:space="preserve">encourage.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8279,14 +8279,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！注目されんのは大歓迎だ！</t>
+          <t xml:space="preserve">止まってられるかよ！次は絶対やってやる！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.delinquent.bold[1]</t>
+          <t xml:space="preserve">faction_decree.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8311,14 +8311,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からいい話来てんだよ。考えさせてくれ</t>
+          <t xml:space="preserve">ふざけんな。あそこは、私らの場所だっただろ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.bold[1]</t>
+          <t xml:space="preserve">media.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8343,14 +8343,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ？やる気出ないっつの。文句あんなら試合組めよ</t>
+          <t xml:space="preserve">注目されんの大歓迎！やってやるぜ！</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.delinquent.bold[1]</t>
+          <t xml:space="preserve">party.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「なんで私らがこんな扱い受けなきゃなんねぇんだよ」とロッカーで吠えている）</t>
+          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.delinquent.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8407,14 +8407,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わる気はねぇから」と宣戦布告じみた投稿）</t>
+          <t xml:space="preserve">充電してくる！戻ったら全開だぜ！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.delinquent.bold[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8439,14 +8439,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトよこせ！今すぐ組め！</t>
+          <t xml:space="preserve">しゃあ！すぐ治して暴れに戻るぜ！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.delinquent.bold[1]</t>
+          <t xml:space="preserve">trainer.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8471,14 +8471,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつと決着つけさせろ！</t>
+          <t xml:space="preserve">最高じゃん！限界まで追い込んでもらうぜ！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.delinquent.bold[1]</t>
+          <t xml:space="preserve">E1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8503,14 +8503,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がもう限界だ。休ませてくれ</t>
+          <t xml:space="preserve">やってやるぜ！注目されんのは大歓迎だ！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.delinquent.bold[1]</t>
+          <t xml:space="preserve">E6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8535,14 +8535,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんじゃやってらんねーよ！改善しろ！</t>
+          <t xml:space="preserve">他所からいい話来てんだよ。考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.delinquent.bold[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8567,14 +8567,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（舌打ちをこらえて、拳を握っている）</t>
+          <t xml:space="preserve">はぁ？やる気出ないっつの。文句あんなら試合組めよ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.delinquent.bold[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8599,14 +8599,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりてぇ！特訓させろ！</t>
+          <t xml:space="preserve">（「なんで私らがこんな扱い受けなきゃなんねぇんだよ」とロッカーで吠えている）</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.delinquent.bold[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8631,14 +8631,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒は任せろ。鍛えてやる</t>
+          <t xml:space="preserve">（SNSに「このまま終わる気はねぇから」と宣戦布告じみた投稿）</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.delinquent.bold[1]</t>
+          <t xml:space="preserve">S1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…こんなとこで止まってらんねえ！</t>
+          <t xml:space="preserve">ベルトよこせ！今すぐ組め！</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.delinquent.bold[1]</t>
+          <t xml:space="preserve">S2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8695,14 +8695,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつの態度が気に食わねえ！限界だ！</t>
+          <t xml:space="preserve">あいつと決着つけさせろ！</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.delinquent.bold[1]</t>
+          <t xml:space="preserve">S3.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8727,14 +8727,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">黙ってると思うなよ！向こうが謝れ！</t>
+          <t xml:space="preserve">くそ…体がもう限界だ。休ませてくれ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.delinquent.bold[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品、派手にやってやる！</t>
+          <t xml:space="preserve">こんなんじゃやってらんねーよ！改善しろ！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.delinquent.bold[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8791,14 +8791,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？ 全国にこの顔を売りつけてやる！</t>
+          <t xml:space="preserve">…………（舌打ちをこらえて、拳を握っている）</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.delinquent.bold[1]</t>
+          <t xml:space="preserve">S5.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8823,14 +8823,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンイベ、盛り上げてやるよ！</t>
+          <t xml:space="preserve">もっと強くなりてぇ！特訓させろ！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.delinquent.bold[1]</t>
+          <t xml:space="preserve">S6.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">歩くだけなら怖くない。ど派手にやってやる</t>
+          <t xml:space="preserve">後輩の面倒は任せろ。鍛えてやる</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.delinquent.bold[1]</t>
+          <t xml:space="preserve">B1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアも勝負事だ。全力でいくよ</t>
+          <t xml:space="preserve">くそっ…こんなとこで止まってらんねえ！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.delinquent.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8919,14 +8919,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビで暴れてやる！ 絶対爪痕残す！</t>
+          <t xml:space="preserve">あいつの態度が気に食わねえ！限界だ！</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.delinquent.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8951,14 +8951,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全国に見せてやるぜ！かかってこい！</t>
+          <t xml:space="preserve">黙ってると思うなよ！向こうが謝れ！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8968,29 +8968,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
+          <t xml:space="preserve">コラボ商品、派手にやってやる！</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9000,29 +9000,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
+          <t xml:space="preserve">CM？ 全国にこの顔を売りつけてやる！</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9032,29 +9032,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">B4_fan.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
+          <t xml:space="preserve">ファンイベ、盛り上げてやるよ！</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9064,29 +9064,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
+          <t xml:space="preserve">歩くだけなら怖くない。ど派手にやってやる</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9096,29 +9096,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
+          <t xml:space="preserve">グラビアも勝負事だ。全力でいくよ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9128,29 +9128,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
+          <t xml:space="preserve">テレビで暴れてやる！ 絶対爪痕残す！</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9160,29 +9160,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">B4.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
+          <t xml:space="preserve">全国に見せてやるぜ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9192,12 +9192,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9207,14 +9207,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう決着はついてんだよ。何度潰されりゃ気が済む</t>
+          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9239,14 +9239,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの日から一度も、まともに寝てねえんだよ</t>
+          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9271,14 +9271,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
+          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9303,14 +9303,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
+          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9335,14 +9335,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
+          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9367,14 +9367,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9399,14 +9399,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
+          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.delinquent.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9431,14 +9431,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
+          <t xml:space="preserve">もう決着はついてんだよ。何度潰されりゃ気が済む</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.delinquent.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9463,14 +9463,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
+          <t xml:space="preserve">あの日から一度も、まともに寝てねえんだよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.delinquent.bold[1]</t>
+          <t xml:space="preserve">draftInterest.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9495,14 +9495,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
+          <t xml:space="preserve">選ぶなら覚悟しろよ。手加減なんかしねえからな</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.delinquent.bold[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9527,14 +9527,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
+          <t xml:space="preserve">暴れまくってやるぜ。覚悟しとけよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.bold[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9559,14 +9559,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
+          <t xml:space="preserve">チャンピオン獲ってやるからな、見とけ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.bold[2]</t>
+          <t xml:space="preserve">faGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9591,14 +9591,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
+          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.bold[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9623,14 +9623,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
+          <t xml:space="preserve">やってやるぜ！暴れまくるからな！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.bold[2]</t>
+          <t xml:space="preserve">faWelcome.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9655,14 +9655,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
+          <t xml:space="preserve">大暴れするぞー！覚悟しとけ！</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9687,14 +9687,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
+          <t xml:space="preserve">力が余ってる感じだ。もっと来い、まだまだ行ける！</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.delinquent.bold[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9719,14 +9719,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
+          <t xml:space="preserve">重ぇ。…けど休まねぇ。休むって言葉が嫌ぇなんだよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">heatSelf.warm.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9751,14 +9751,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
+          <t xml:space="preserve">まだいけるって。…ちょい鈍ってるだけだ、これは</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.delinquent.bold[1]</t>
+          <t xml:space="preserve">injury.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
+          <t xml:space="preserve">ちくしょう…！ ぜってぇ戻ってくるからな！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.delinquent.bold[1]</t>
+          <t xml:space="preserve">injury.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9815,14 +9815,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
+          <t xml:space="preserve">こんなんで終わってたまるかよ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">release.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9847,14 +9847,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
+          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">release.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9879,14 +9879,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
+          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9911,14 +9911,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
+          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9943,14 +9943,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
+          <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9982,7 +9982,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10014,7 +10014,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">titleWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10078,7 +10078,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10088,29 +10088,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">虫が好かねぇんだよ</t>
+          <t xml:space="preserve">ちくしょう…見とけよ、絶対に戻ってくるからな</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10120,29 +10120,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近態度おかしくね？ ムカつくな</t>
+          <t xml:space="preserve">悔しいぜ…次の場所でぶっちぎってやる</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10152,29 +10152,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見込みあるよ。面倒見てやるか</t>
+          <t xml:space="preserve">レンタル？ 関係ねえ！暴れるぞ！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10184,29 +10184,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フン、気に入ったぜ</t>
+          <t xml:space="preserve">こんなの認めねえ！もう一回だ！</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10216,29 +10216,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒だ。文句あるか</t>
+          <t xml:space="preserve">まだまだ負けるわけねーだろ！かかってこい！</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10248,29 +10248,29 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時代は終わりだ。もう眼中にねぇ</t>
+          <t xml:space="preserve">こんなの認めねえ！絶対取り返す！</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10280,29 +10280,29 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面ぁ見ると血が騒ぐんだよ</t>
+          <t xml:space="preserve">やっと獲ったぜ！次は誰が来ても負けねえ！</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10327,14 +10327,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">這いつくばらせてやる…！</t>
+          <t xml:space="preserve">虫が好かねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10359,14 +10359,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">生涯の敵だ。最後まで殴り合ってやる</t>
+          <t xml:space="preserve">おい、最近態度おかしくね？ ムカつくな</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10391,14 +10391,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは最高だ。私がてっぺんまで連れてってやるよ</t>
+          <t xml:space="preserve">見込みあるよ。面倒見てやるか</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.delinquent[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.delinquent[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10423,14 +10423,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を舐めてんなら出てってやるよ。後悔するなよ</t>
+          <t xml:space="preserve">フン、気に入ったぜ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10455,14 +10455,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なめんじゃねぇぞ。私をもっと使え</t>
+          <t xml:space="preserve">相棒だ。文句あるか</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.delinquent.bold[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10487,14 +10487,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次会ったらぶっ飛ばしてやる…覚えてろ</t>
+          <t xml:space="preserve">時代は終わりだ。もう眼中にねぇ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.delinquent.bold[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10519,14 +10519,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へっ、雑魚が。話にならねぇ</t>
+          <t xml:space="preserve">面ぁ見ると血が騒ぐんだよ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.delinquent.bold[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10551,14 +10551,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おらおら、休んでる暇ねぇぞ！</t>
+          <t xml:space="preserve">這いつくばらせてやる…！</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.delinquent.bold[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10583,14 +10583,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダチだ。大事にしてやるよ</t>
+          <t xml:space="preserve">生涯の敵だ。最後まで殴り合ってやる</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.delinquent.bold[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10615,14 +10615,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えるまで止まらねぇ</t>
+          <t xml:space="preserve">ここは最高だ。私がてっぺんまで連れてってやるよ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.delinquent.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10647,14 +10647,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おいこら！ 私を出せよ！ 暴れたいんだよ！</t>
+          <t xml:space="preserve">私を舐めてんなら出てってやるよ。後悔するなよ</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.delinquent.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.delinquent[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10679,14 +10679,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ、こんな体じゃ戦えねぇだろ…！</t>
+          <t xml:space="preserve">なめんじゃねぇぞ。私をもっと使え</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-01.loss.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10711,14 +10711,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…いつまで負けてんだよ…！</t>
+          <t xml:space="preserve">次会ったらぶっ飛ばしてやる…覚えてろ</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-01.win.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10743,14 +10743,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止まらねぇぜ！ 全員ぶっ倒す！</t>
+          <t xml:space="preserve">へっ、雑魚が。話にならねぇ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10775,14 +10775,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ…じっとしてらんねぇ。もう走れるだろ…！</t>
+          <t xml:space="preserve">おらおら、休んでる暇ねぇぞ！</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10807,14 +10807,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子戻っちまったけど、あの感覚は覚えたぜ</t>
+          <t xml:space="preserve">ダチだ。大事にしてやるよ</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10824,29 +10824,29 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体？ 知るかよ。最後まで残ったんだ、テッペン獲るに決まってんだろ</t>
+          <t xml:space="preserve">超えるまで止まらねぇ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10856,29 +10856,29 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">GL-06.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボロボロだろうが関係ねえ。この一戦、ぶっ潰して終わらせる</t>
+          <t xml:space="preserve">おいこら！ 私を出せよ！ 暴れたいんだよ！</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10888,29 +10888,29 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[3]</t>
+          <t xml:space="preserve">GL-07.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">痛え？ あたりめえだろ。でもここで倒れたら、今までが無駄になる。行くぞ</t>
+          <t xml:space="preserve">くそっ、こんな体じゃ戦えねぇだろ…！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10920,29 +10920,29 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ！ 何人来ようがまとめてかかってこいや</t>
+          <t xml:space="preserve">ふざけんな…いつまで負けてんだよ…！</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10952,29 +10952,29 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">GL-09.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ずつしか来れねえのか？ じれってえな。全員まとめて潰してやる</t>
+          <t xml:space="preserve">止まらねぇぜ！ 全員ぶっ倒す！</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10984,29 +10984,29 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[3]</t>
+          <t xml:space="preserve">GL-10.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、渡すわけねえだろ。出てこいよ、順番に沈めてやる</t>
+          <t xml:space="preserve">チッ…じっとしてらんねぇ。もう走れるだろ…！</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11016,29 +11016,29 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ぶっ倒した！ …はぁ、まだいけるぞ。次、どいつだ、出てこい！</t>
+          <t xml:space="preserve">調子戻っちまったけど、あの感覚は覚えたぜ</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.bold[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11063,14 +11063,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえ！ このリング、渡すかよ。次、さっさとかかってこい！</t>
+          <t xml:space="preserve">身体？ 知るかよ。最後まで残ったんだ、テッペン獲るに決まってんだろ</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.bold[3]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11095,14 +11095,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人沈めたぞ！ …はぁ、はぁ…まだ足りねえ。次、誰でもいい、来い！</t>
+          <t xml:space="preserve">ボロボロだろうが関係ねえ。この一戦、ぶっ潰して終わらせる</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11127,14 +11127,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私らが最強だ。文句あんなら、かかってこいよ</t>
+          <t xml:space="preserve">痛え？ あたりめえだろ。でもここで倒れたら、今までが無駄になる。行くぞ</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11144,12 +11144,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11159,14 +11159,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人揃って無敵だったな。最高のチームだぜ</t>
+          <t xml:space="preserve">相手は誰だ！ 何人来ようがまとめてかかってこいや</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11176,12 +11176,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.bold[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11191,14 +11191,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ はっ、こんなもんじゃ足りねえよ。次は丸ごとぶん取る</t>
+          <t xml:space="preserve">一人ずつしか来れねえのか？ じれってえな。全員まとめて潰してやる</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.bold[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11223,14 +11223,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっとくけど、次は優勝旗ごと叩き取る。覚えとけ</t>
+          <t xml:space="preserve">このリング、渡すわけねえだろ。出てこいよ、順番に沈めてやる</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.bold[1]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11255,14 +11255,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るだけ来いっつったろ？ 全員ぶっ倒して、まだ余裕あんぞ</t>
+          <t xml:space="preserve">一人ぶっ倒した！ …はぁ、まだいけるぞ。次、どいつだ、出てこい！</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.bold[2]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人並ぼうが一緒だ。私の前に立つなら覚悟しろ</t>
+          <t xml:space="preserve">まだ終わってねえ！ このリング、渡すかよ。次、さっさとかかってこい！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[1]</t>
+          <t xml:space="preserve">survivor.delinquent.bold[3]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11319,14 +11319,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったろ？ テッペンは私のもんだってな</t>
+          <t xml:space="preserve">一人沈めたぞ！ …はぁ、はぁ…まだ足りねえ。次、誰でもいい、来い！</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.bold[2]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11351,14 +11351,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、当然の結果だぜ。誰にも負けねえ</t>
+          <t xml:space="preserve">私らが最強だ。文句あんなら、かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.bold[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11383,14 +11383,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…！ 次は絶対ぶっ潰す！</t>
+          <t xml:space="preserve">三人揃って無敵だったな。最高のチームだぜ</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.bold[2]</t>
+          <t xml:space="preserve">defiant.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11415,14 +11415,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなん認めねえ…！</t>
+          <t xml:space="preserve">MVP？ はっ、こんなもんじゃ足りねえよ。次は丸ごとぶん取る</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">defiant.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11447,14 +11447,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、楽勝だぜ。次も同じだ</t>
+          <t xml:space="preserve">賞はもらっとくけど、次は優勝旗ごと叩き取る。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11479,14 +11479,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">止められるもんなら止めてみろ</t>
+          <t xml:space="preserve">来るだけ来いっつったろ？ 全員ぶっ倒して、まだ余裕あんぞ</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.bold[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11511,14 +11511,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ、まだ足りねえ。次は全員ぶっ倒す</t>
+          <t xml:space="preserve">何人並ぼうが一緒だ。私の前に立つなら覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.bold[2]</t>
+          <t xml:space="preserve">champion.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11543,14 +11543,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ上がいるってのがムカつくぜ</t>
+          <t xml:space="preserve">言ったろ？ テッペンは私のもんだってな</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
+          <t xml:space="preserve">champion.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11575,14 +11575,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たからにゃ、テッペン獲るに決まってんだろ</t>
+          <t xml:space="preserve">はっ、当然の結果だぜ。誰にも負けねえ</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
+          <t xml:space="preserve">postLose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11607,14 +11607,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の相手か。ぶっ壊してやるよ</t>
+          <t xml:space="preserve">ふざけんな…！ 次は絶対ぶっ潰す！</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
+          <t xml:space="preserve">postLose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11639,14 +11639,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">邪魔するヤツは全員ぶっ倒す</t>
+          <t xml:space="preserve">こんなん認めねえ…！</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11671,14 +11671,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かかって来いよ。一発で沈めてやる</t>
+          <t xml:space="preserve">はっ、楽勝だぜ。次も同じだ</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11703,14 +11703,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あァ？ まあいいけど。暴れる場所が増えるだけだ</t>
+          <t xml:space="preserve">止められるもんなら止めてみろ</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.bold[2]</t>
+          <t xml:space="preserve">postWin.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11735,14 +11735,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっせーな、勝手に呼びやがって。……まあ出るけど</t>
+          <t xml:space="preserve">ちっ、まだ足りねえ。次は全員ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">postWin.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11767,14 +11767,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰してやるぜ！泣いても知らねーぞ！</t>
+          <t xml:space="preserve">まだ上がいるってのがムカつくぜ</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11799,14 +11799,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぞ……！ 全員ぶっ倒してここまで来たんだ……！</t>
+          <t xml:space="preserve">ここまで来たからにゃ、テッペン獲るに決まってんだろ</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11831,14 +11831,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てめえらの団体？ うちの新人にも勝てねえだろ</t>
+          <t xml:space="preserve">最後の相手か。ぶっ壊してやるよ</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11848,12 +11848,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11863,14 +11863,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰してやるよ。覚悟しろ</t>
+          <t xml:space="preserve">邪魔するヤツは全員ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、ザッコ。逃げんのかよ</t>
+          <t xml:space="preserve">かかって来いよ。一発で沈めてやる</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">summon.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11927,14 +11927,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次会った時は逃がさねえからな。覚えとけ</t>
+          <t xml:space="preserve">あァ？ まあいいけど。暴れる場所が増えるだけだ</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.bold[1]</t>
+          <t xml:space="preserve">summon.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11959,14 +11959,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…マジかよ…。絶対リベンジしてやる</t>
+          <t xml:space="preserve">うっせーな、勝手に呼びやがって。……まあ出るけど</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11991,14 +11991,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな…次はぶっ壊してやるからな</t>
+          <t xml:space="preserve">ぶっ潰してやるぜ！泣いても知らねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -12023,14 +12023,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、楽勝だぜ。雑魚が調子乗んなよ</t>
+          <t xml:space="preserve">やったぞ……！ 全員ぶっ倒してここまで来たんだ……！</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12055,14 +12055,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがウチの強さだ。分かったか</t>
+          <t xml:space="preserve">てめえらの団体？ うちの新人にも勝てねえだろ</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12087,14 +12087,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然だろ！ うちの団体なめんじゃねえよ！</t>
+          <t xml:space="preserve">ぶっ潰してやるよ。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[2]</t>
+          <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -12119,14 +12119,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ざまあみろ！ これがうちの実力だ！</t>
+          <t xml:space="preserve">はっ、ザッコ。逃げんのかよ</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12136,12 +12136,12 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[3]</t>
+          <t xml:space="preserve">delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12151,14 +12151,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体に手ぇ出すからだ。ざまぁみろ</t>
+          <t xml:space="preserve">次会った時は逃がさねえからな。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12168,29 +12168,29 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.bold[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.bold[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲ったぜ！でもまだまだこれからだ！</t>
+          <t xml:space="preserve">ちっ…マジかよ…。絶対リベンジしてやる</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12200,59 +12200,283 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.bold[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.bold[2]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+          <t xml:space="preserve">ふざけんな…次はぶっ壊してやるからな</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はっ、楽勝だぜ。雑魚が調子乗んなよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="40" customHeight="1">
+      <c r="A370" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.bold[2]</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.bold[2]</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これがウチの強さだ。分かったか</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="40" customHeight="1">
+      <c r="A371" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然だろ！ うちの団体なめんじゃねえよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="40" customHeight="1">
+      <c r="A372" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[2]</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.bold[2]</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ざまあみろ！ これがうちの実力だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="40" customHeight="1">
+      <c r="A373" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.bold[3]</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.bold[3]</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うちの団体に手ぇ出すからだ。ざまぁみろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="40" customHeight="1">
+      <c r="A374" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">てっぺん獲ったぜ！でもまだまだこれからだ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="40" customHeight="1">
+      <c r="A375" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.bold[1]</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">干されてた女がどこまで行くか、見てろよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="40" customHeight="1">
+      <c r="A376" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr" s="2">
+      <c r="B376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr" s="12">
+      <c r="D376" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.bold[1]</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr" s="2">
+      <c r="E376" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr" s="3">
+      <c r="F376" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あんたが見つけた私が当たりかどうか。見てなよ。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H369"/>
+  <autoFilter ref="A1:H376"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
@@ -2579,7 +2579,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あいつとやらせてくださいよ。勝てるんで。</t>
+          <t xml:space="preserve">社長、三人で乗り込ませてくださいよ。勝てるんで。</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとやりたいんす。……頼みます、組んでください。</t>
+          <t xml:space="preserve">あの団体とやりたいんす。……頼みます、三人で組んでください。</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言わなきゃ回ってこねぇんで、直接来ました。お願いします。</t>
+          <t xml:space="preserve">言わなきゃ回ってこねぇんで、直接来ました。三人で行かせてください。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×強気.xlsx
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしんとこも、舐められたまま終わる気はねえ</t>
+          <t xml:space="preserve">私んとこも、舐められたまま終わる気はねえ</t>
         </is>
       </c>
     </row>
